--- a/ecoenergy/EcoEnergy_Aggregate_Sales_Pipeline.xlsx
+++ b/ecoenergy/EcoEnergy_Aggregate_Sales_Pipeline.xlsx
@@ -130,7 +130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -175,7 +175,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 1   |   12 September 2026  02:04 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 2   |   12 September 2026  02:13 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aggregate wholesaler/supplier</t>
+          <t xml:space="preserve">Aggregate supplier / equipment</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trinidad</t>
+          <t xml:space="preserve">Charlieville</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING VERIFICATION</t>
+          <t xml:space="preserve">868-750-1625</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -1143,7 +1143,7 @@
       <c r="Y11" s="7"/>
       <c r="Z11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISCOVERED</t>
+          <t xml:space="preserve">CONTACT AVAILABLE</t>
         </is>
       </c>
       <c r="AA11" s="7"/>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="AC11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify direct telephone/e-mail from company website, then issue wholesale introduction letter and current price list. Strong wholesale-supply fit - lead with reseller margin.</t>
+          <t xml:space="preserve">Telephone 868-750-1625 and open the wholesale supply conversation. Contact route is live, so this no longer needs detail verification.</t>
         </is>
       </c>
       <c r="AD11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name indicates a pure aggregate supply business, so it must buy from a quarry. High-fit wholesale prospect. Directory page blocked by egress policy - contact details not retrieved.</t>
+          <t xml:space="preserve">Name indicates a pure aggregate supply business, so it must buy from a quarry. High-fit wholesale prospect. Directory page blocked by egress policy - contact details not retrieved. | MERGED 2026-09-12 from the prior EcoEnergy workbook: telephone 868-750-1625 and Charlieville location supplied by prior canon. Prior record listed this as an aggregate/paving materials supplier with no published price, priority Medium. Duplicate avoided per section 10.</t>
         </is>
       </c>
     </row>
@@ -7051,29 +7051,1667 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0049</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On The Line General Hardware</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chaguanas / Felicity</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242-4699 / 234-4949</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">796-1337 / 469-9178</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior EcoEnergy workbook (merged 2026-09-12)</t>
+        </is>
+      </c>
+      <c r="Q54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.equipment10.com/TT/Chaguanas/1915323488711905/On-The-Line-General-Hardware</t>
+        </is>
+      </c>
+      <c r="R54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advertises plastering sand and gravel by the load - an active aggregate reseller.</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plastering sand; gravel</t>
+        </is>
+      </c>
+      <c r="T54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plastering sand; gravel</t>
+        </is>
+      </c>
+      <c r="U54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="V54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="W54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plastering sand TT$1,200/load; gravel TT$2,350/load</t>
+        </is>
+      </c>
+      <c r="X54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTACT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA54" s="7"/>
+      <c r="AB54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telephone and open the wholesale supply conversation. Contact route is live. Load pricing is published, so the reseller spread can be quantified before the call.</t>
+        </is>
+      </c>
+      <c r="AD54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Wholesale/repeat reseller supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0050</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NARS Value Hardware</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Juan</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">625-7326</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">747-6941 / 332-5433</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior EcoEnergy workbook (merged 2026-09-12)</t>
+        </is>
+      </c>
+      <c r="Q55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.findglocal.com/TT/San-Juan/1797123157231816/NARS-Value-Hardware-Ltd</t>
+        </is>
+      </c>
+      <c r="R55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publishes per-yard retail prices across three EcoEnergy lines - a confirmed reseller.</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel; sharp sand; plastering sand</t>
+        </is>
+      </c>
+      <c r="T55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel; sharp sand; plastering sand</t>
+        </is>
+      </c>
+      <c r="U55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="V55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="W55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel TT$350/yd; sharp sand TT$450/yd; plastering sand TT$250/yd</t>
+        </is>
+      </c>
+      <c r="X55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTACT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA55" s="7"/>
+      <c r="AB55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telephone and open the wholesale supply conversation. Contact route is live. Their sharp sand retails at TT$450/yd against an EcoEnergy base of TT$167.06, so lead with the spread.</t>
+        </is>
+      </c>
+      <c r="AD55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Large reseller margin possible</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0051</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad Quarry Materials</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate reseller / delivery</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sangre Grande</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868-704-6438</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior EcoEnergy workbook (merged 2026-09-12)</t>
+        </is>
+      </c>
+      <c r="Q56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.findglocal.com/TT/Sangre-Grande-Town/106173400997686/Trinidad-Quarry-Materials</t>
+        </is>
+      </c>
+      <c r="R56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sells gravel, plastering sand, backfill and crusher run by the load with delivery.</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel; plastering sand; backfill; crusher run</t>
+        </is>
+      </c>
+      <c r="T56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel; plastering sand; backfill; crusher run</t>
+        </is>
+      </c>
+      <c r="U56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="V56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="W56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel TT$1,800/load; plastering sand TT$1,400/load</t>
+        </is>
+      </c>
+      <c r="X56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTACT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA56" s="7"/>
+      <c r="AB56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telephone and open the wholesale supply conversation. Contact route is live. Also qualify as an overflow supply source, not only as a buyer.</t>
+        </is>
+      </c>
+      <c r="AD56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Wholesale supply / overflow source</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0052</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMCOL Hardware</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penal</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">647-7653</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior EcoEnergy workbook (merged 2026-09-12)</t>
+        </is>
+      </c>
+      <c r="Q57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.amcolhardwarett.com/search.php?category=Construction+Aggregate</t>
+        </is>
+      </c>
+      <c r="R57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publishes an online construction aggregate catalogue including mixes, backfill and sandfill.</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate; gravel/sand mixes; backfill; sandfill</t>
+        </is>
+      </c>
+      <c r="T57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate; gravel/sand mixes; backfill; sandfill</t>
+        </is>
+      </c>
+      <c r="U57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="V57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="W57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/8 mix 8yd TT$2,300; 10yd aggregate mix TT$3,000; sharp sand TT$440/yd</t>
+        </is>
+      </c>
+      <c r="X57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTACT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA57" s="7"/>
+      <c r="AB57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telephone and open the wholesale supply conversation. Contact route is live. Their published catalogue is also the benchmark source for backfill and sand fill, so keep it monitored.</t>
+        </is>
+      </c>
+      <c r="AD57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Strong reseller prospect</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0053</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cumosco</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Online hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad &amp; Tobago</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868-689-3606</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sales@cumosco.com</t>
+        </is>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior EcoEnergy workbook (merged 2026-09-12)</t>
+        </is>
+      </c>
+      <c r="Q58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.cumosco.com/product/gravel/</t>
+        </is>
+      </c>
+      <c r="R58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sells gravel online at TT$300/yd. Already contacted by EcoEnergy.</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel; sand</t>
+        </is>
+      </c>
+      <c r="T58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel; sand</t>
+        </is>
+      </c>
+      <c r="U58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="V58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="W58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel TT$300/yd</t>
+        </is>
+      </c>
+      <c r="X58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUTREACH SENT</t>
+        </is>
+      </c>
+      <c r="AA58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORRECTED QUOTATION REQUIRED. The e-mail of 2026-09-12 quoted TT$125 / 195 / 205 per yd3 for pitrun / 3/8 / 3/4. All three sit ABOVE the canon list price of TT$77.63 / 167.06 / 167.06. Issue a corrected quotation at list before any follow-up.</t>
+        </is>
+      </c>
+      <c r="AD58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches. PRICING EXCEPTION - see COMMUNICATIONS LOG and the corrected-quotation action. EcoEnergy opportunity as previously assessed: Wholesale supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0054</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KAMCO Marketing &amp; Contracting</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procurement / contractor</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Fernando</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868-755-1702</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kamcomarketing2014@gmail.com</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior EcoEnergy workbook (merged 2026-09-12)</t>
+        </is>
+      </c>
+      <c r="Q59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://kmclglobal.com/</t>
+        </is>
+      </c>
+      <c r="R59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Construction materials procurement business. Already contacted by EcoEnergy.</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Construction materials procurement</t>
+        </is>
+      </c>
+      <c r="T59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Construction materials procurement</t>
+        </is>
+      </c>
+      <c r="U59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="V59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="W59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quote-based</t>
+        </is>
+      </c>
+      <c r="X59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUTREACH SENT</t>
+        </is>
+      </c>
+      <c r="AA59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow up on the 2026-09-12 introduction and qualify material and volume. No price was quoted, so no correction is needed.</t>
+        </is>
+      </c>
+      <c r="AD59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Project/contract supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0055</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Southern Aggregate and Supplies Ltd</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Fernando</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868-271-9382</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior EcoEnergy workbook (merged 2026-09-12)</t>
+        </is>
+      </c>
+      <c r="Q60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business listing (prior workbook)</t>
+        </is>
+      </c>
+      <c r="R60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named as an aggregate and building materials supplier - buys aggregate to resell.</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate / building materials</t>
+        </is>
+      </c>
+      <c r="T60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate / building materials</t>
+        </is>
+      </c>
+      <c r="U60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="V60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="W60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTACT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA60" s="7"/>
+      <c r="AB60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telephone and open the wholesale supply conversation. Contact route is live.</t>
+        </is>
+      </c>
+      <c r="AD60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Wholesale reseller</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0056</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">James Transport</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate supplier / trucking</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diego Martin</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868-633-7144</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior EcoEnergy workbook (merged 2026-09-12)</t>
+        </is>
+      </c>
+      <c r="Q61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business listing (prior workbook)</t>
+        </is>
+      </c>
+      <c r="R61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Combines aggregate supply with transport - both a buyer and a delivery partner.</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate supply / transport</t>
+        </is>
+      </c>
+      <c r="T61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate supply / transport</t>
+        </is>
+      </c>
+      <c r="U61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="V61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="W61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTACT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA61" s="7"/>
+      <c r="AB61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telephone and open the wholesale supply conversation. Contact route is live. Qualify for both material supply and haulage capacity.</t>
+        </is>
+      </c>
+      <c r="AD61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Distribution / trucking / resale</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0057</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gibson's Hardware</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials supplier</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aripero</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868-651-1033</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior EcoEnergy workbook (merged 2026-09-12)</t>
+        </is>
+      </c>
+      <c r="Q62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business listing (prior workbook)</t>
+        </is>
+      </c>
+      <c r="R62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials supplier in south Trinidad.</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials</t>
+        </is>
+      </c>
+      <c r="T62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials</t>
+        </is>
+      </c>
+      <c r="U62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="V62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="W62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTACT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA62" s="7"/>
+      <c r="AB62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telephone and open the wholesale supply conversation. Contact route is live.</t>
+        </is>
+      </c>
+      <c r="AD62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Reseller supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0058</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K&amp;S Hardware and Plumbing Supplies</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials store</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cunupia</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868-219-3689</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior EcoEnergy workbook (merged 2026-09-12)</t>
+        </is>
+      </c>
+      <c r="Q63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business listing (prior workbook)</t>
+        </is>
+      </c>
+      <c r="R63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials store in the central construction corridor.</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials</t>
+        </is>
+      </c>
+      <c r="T63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials</t>
+        </is>
+      </c>
+      <c r="U63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="V63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="W63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTACT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA63" s="7"/>
+      <c r="AB63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telephone and open the wholesale supply conversation. Contact route is live.</t>
+        </is>
+      </c>
+      <c r="AD63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Reseller supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0059</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seupersad's Y Junction Hardware</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials supplier</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claxton Bay</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868-348-4020</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior EcoEnergy workbook (merged 2026-09-12)</t>
+        </is>
+      </c>
+      <c r="Q64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business listing (prior workbook)</t>
+        </is>
+      </c>
+      <c r="R64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials supplier.</t>
+        </is>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials</t>
+        </is>
+      </c>
+      <c r="T64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials</t>
+        </is>
+      </c>
+      <c r="U64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="V64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated - to establish on contact</t>
+        </is>
+      </c>
+      <c r="W64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTACT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA64" s="7"/>
+      <c r="AB64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telephone and open the wholesale supply conversation. Contact route is live.</t>
+        </is>
+      </c>
+      <c r="AD64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Reseller supply</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:AD53"/>
+  <autoFilter ref="A5:AD64"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="40" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="60" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7086,14 +8724,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 1   |   12 September 2026  02:04 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 2   |   12 September 2026  02:13 (Trinidad time)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A message is recorded here ONLY when a sending tool confirmed the send.</t>
+          <t xml:space="preserve">A message is recorded here ONLY when a send was confirmed. The two entries below are prior canon carried forward from the previous EcoEnergy workbook.</t>
         </is>
       </c>
     </row>
@@ -7121,69 +8759,203 @@
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Direction</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Recipient</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Message Type</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Material</t>
         </is>
       </c>
-      <c r="H5" s="1" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Volume</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Price Quoted</t>
         </is>
       </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="K5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Discount Mentioned</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="L5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Response</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
+      <c r="M5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Follow-Up Date</t>
         </is>
       </c>
-      <c r="L5" s="1" t="inlineStr">
+      <c r="N5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Next Action</t>
         </is>
       </c>
-      <c r="M5" s="1" t="inlineStr">
+      <c r="O5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Logged By</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0053</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cumosco</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Email</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outbound</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sales@cumosco.com</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wholesale aggregate supply introduction</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8; 3/4</t>
+        </is>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$125 / 195 / 205 per yd3</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORRECTED QUOTATION REQUIRED before follow-up. Quoted prices sit above the canon list price of TT$77.63 / 167.06 / 167.06 per yd3.</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior canon - Outlook Sent Items</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO OUTREACH EXECUTED THIS CYCLE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zero messages have been sent. No e-mail, WhatsApp or messaging integration was authorised or available to this agent, and no verified recipient address was captured, so nothing could be sent and nothing is recorded as sent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Status for all 48 prospects: PROSPECT IDENTIFIED - DIRECT OUTREACH PENDING.</t>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0054</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KAMCO Marketing &amp; Contracting</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Email</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outbound</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kamcomarketing2014@gmail.com</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Individualised EcoEnergy supply introduction</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate</t>
+        </is>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Market-based</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow up and qualify material and volume.</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior canon - Outlook send action</t>
         </is>
       </c>
     </row>
@@ -7193,7 +8965,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -7204,8 +8976,9 @@
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="9" width="46" customWidth="1"/>
-    <col min="10" max="10" width="70" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="46" customWidth="1"/>
+    <col min="11" max="11" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7218,7 +8991,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 1   |   12 September 2026  02:04 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 2   |   12 September 2026  02:13 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -7273,10 +9046,15 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Last Verified</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Benchmark Source</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="K5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Note</t>
         </is>
@@ -7285,22 +9063,22 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4 gravel</t>
+          <t xml:space="preserve">Pitrun</t>
         </is>
       </c>
       <c r="B6" s="4">
-        <v>185.62</v>
+        <v>86.25</v>
       </c>
       <c r="C6" s="4">
-        <v>167.06</v>
+        <v>77.63</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">per cubic yard (VAT incl.)</t>
+          <t xml:space="preserve">TT$/yd3 (collection)</t>
         </is>
       </c>
       <c r="E6" s="4">
-        <v>116.94</v>
+        <v>54.34</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -7309,29 +9087,34 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOW</t>
+          <t xml:space="preserve">MEDIUM</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL - SINGLE SOURCE</t>
+          <t xml:space="preserve">ACTIVE - STALE BENCHMARK</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://buildwithabs.com/product/bulk-aggregate/</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derived from ONE verified source. The brief calls for multiple observations per material; only one credible published T&amp;T source was reachable this cycle. Treat as provisional and re-derive once a second source is obtained.</t>
+          <t xml:space="preserve">https://nqcl.co.tt/wp-content/uploads/NQCL-Price-List-2025.pdf</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NQCL official published list. The document is effective 31-Aug-2022 and carries +12.5% VAT, so the benchmark is four years old. Retained per prior canon and per section 7, which requires the last verified price to be kept when no fresher evidence exists. Re-verify at the next review. Exact unrounded values: base 77.625000, floor 54.337500; published figures are rounded half-up to 2dp for commercial use.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/8 gravel</t>
+          <t xml:space="preserve">3/8 Gravel</t>
         </is>
       </c>
       <c r="B7" s="4">
@@ -7342,7 +9125,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">per cubic yard (VAT incl.)</t>
+          <t xml:space="preserve">TT$/yd3 (collection)</t>
         </is>
       </c>
       <c r="E7" s="4">
@@ -7355,29 +9138,34 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOW</t>
+          <t xml:space="preserve">MEDIUM</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL - SINGLE SOURCE</t>
+          <t xml:space="preserve">ACTIVE</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">https://buildwithabs.com/product/bulk-aggregate/</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Derived from ONE verified source. The brief calls for multiple observations per material; only one credible published T&amp;T source was reachable this cycle. Treat as provisional and re-derive once a second source is obtained.</t>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bestcrete/Aggre GO current public bulk price, VAT inclusive. Strong directly comparable benchmark. Exact unrounded values: base 167.058000, floor 116.940600; published figures are rounded half-up to 2dp for commercial use.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharp sand</t>
+          <t xml:space="preserve">3/4 Gravel</t>
         </is>
       </c>
       <c r="B8" s="4">
@@ -7388,7 +9176,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">per cubic yard (VAT incl.)</t>
+          <t xml:space="preserve">TT$/yd3 (collection)</t>
         </is>
       </c>
       <c r="E8" s="4">
@@ -7401,44 +9189,49 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOW</t>
+          <t xml:space="preserve">MEDIUM</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL - SINGLE SOURCE</t>
+          <t xml:space="preserve">ACTIVE</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">https://buildwithabs.com/product/bulk-aggregate/</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Derived from ONE verified source. The brief calls for multiple observations per material; only one credible published T&amp;T source was reachable this cycle. Treat as provisional and re-derive once a second source is obtained.</t>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bestcrete/Aggre GO current public bulk price, VAT inclusive. Strong directly comparable benchmark. Exact unrounded values: base 167.058000, floor 116.940600; published figures are rounded half-up to 2dp for commercial use.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plastering sand</t>
+          <t xml:space="preserve">Sharp Sand</t>
         </is>
       </c>
       <c r="B9" s="4">
-        <v>84.38</v>
+        <v>185.62</v>
       </c>
       <c r="C9" s="4">
-        <v>75.94</v>
+        <v>167.06</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">per cubic yard (VAT incl.)</t>
+          <t xml:space="preserve">TT$/yd3 (collection)</t>
         </is>
       </c>
       <c r="E9" s="4">
-        <v>53.16</v>
+        <v>116.94</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -7447,50 +9240,49 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOW</t>
+          <t xml:space="preserve">MEDIUM</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL - SINGLE SOURCE</t>
+          <t xml:space="preserve">ACTIVE</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">https://buildwithabs.com/product/bulk-aggregate/</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Derived from ONE verified source. The brief calls for multiple observations per material; only one credible published T&amp;T source was reachable this cycle. Treat as provisional and re-derive once a second source is obtained.</t>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bestcrete/Aggre GO current public bulk price, VAT inclusive. NARS retail is TT$450/yd3 and Cumosco TT$300/yd3, which shows the reseller spread available. Exact unrounded values: base 167.058000, floor 116.940600; published figures are rounded half-up to 2dp for commercial use.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pitrun</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO DATA</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOT SET</t>
-        </is>
+          <t xml:space="preserve">Plastering Sand</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <v>84.38</v>
+      </c>
+      <c r="C10" s="4">
+        <v>75.94</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">per cubic yard</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n/a</t>
-        </is>
+          <t xml:space="preserve">TT$/yd3 (collection)</t>
+        </is>
+      </c>
+      <c r="E10" s="4">
+        <v>53.16</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -7499,50 +9291,49 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">MEDIUM</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARKET VERIFICATION REQUIRED</t>
+          <t xml:space="preserve">ACTIVE</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">No verified T&amp;T published price located this cycle</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO PRICE SET. No published T&amp;T pitrun price was found. Per section 7 no price is invented and no stale price exists to retain. Highest-priority pricing gap - pitrun is a core EcoEnergy line.</t>
+          <t xml:space="preserve">https://buildwithabs.com/product/bulk-aggregate/</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bestcrete collection price, VAT inclusive. Pine Road Matura collection is TT$67.50/yd3, so quote location-specific where relevant. Exact unrounded values: base 75.942000, floor 53.159400; published figures are rounded half-up to 2dp for commercial use.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandfill / backfill</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO DATA</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOT SET</t>
-        </is>
+          <t xml:space="preserve">Backfill / Overburden</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <v>140.625</v>
+      </c>
+      <c r="C11" s="4">
+        <v>126.56</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">per cubic yard</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n/a</t>
-        </is>
+          <t xml:space="preserve">TT$/yd3</t>
+        </is>
+      </c>
+      <c r="E11" s="4">
+        <v>88.59</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -7551,50 +9342,106 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">MEDIUM</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARKET VERIFICATION REQUIRED</t>
+          <t xml:space="preserve">ACTIVE - RETAIL BASIS</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">No verified T&amp;T published price located this cycle</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO PRICE SET. No published T&amp;T sandfill/backfill price was found. Second-highest pricing gap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+          <t xml:space="preserve">https://www.amcolhardwarett.com/search.php?category=Construction+Aggregate</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMCOL 8-yard load TT$1,125 = TT$140.625/yd3. Likely a retail or delivered context, so not directly ex-quarry comparable. Treat the base as indicative until an ex-quarry observation is obtained. Exact unrounded values: base 126.562500, floor 88.593750; published figures are rounded half-up to 2dp for commercial use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand Fill</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <v>126.563</v>
+      </c>
+      <c r="C12" s="4">
+        <v>113.91</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$/yd3</t>
+        </is>
+      </c>
+      <c r="E12" s="4">
+        <v>79.73</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDIUM</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACTIVE - RETAIL BASIS</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.amcolhardwarett.com/search.php?category=Construction+Aggregate</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMCOL 10-yard load TT$1,265.63 = TT$126.563/yd3. Likely a retail or delivered context. Exact unrounded values: base 113.906700, floor 79.734690; published figures are rounded half-up to 2dp for commercial use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">CUSTOMER-FACING STATEMENT</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Wholesale, cash-volume and contracted recurring customers may qualify for additional negotiated volume discounts of up to 30%.</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">INTERNAL - DO NOT PUBLISH</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Negotiated Floor column is the maximum 30% concession and is a closing tool, not a list price. It is never offered automatically and never advertised. Award it against quantity, frequency, payment method and speed, collection versus delivery, trucking economics, contract duration, lifetime value and reseller potential.</t>
         </is>
@@ -7606,7 +9453,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -7632,7 +9479,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 1   |   12 September 2026  02:04 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 2   |   12 September 2026  02:13 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -8151,63 +9998,786 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full product range</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
+          <t xml:space="preserve">Pitrun</t>
+        </is>
+      </c>
+      <c r="C14" s="4">
+        <v>86.25</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$/yd3</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official state published list</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EX-QUARRY (STATE)</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collection</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guaico, Sangre Grande</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://nqcl.co.tt/wp-content/uploads/NQCL-Price-List-2025.pdf</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recovered from prior canon. Document effective 31-Aug-2022 plus 12.5% VAT - four years old.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NARS Value Hardware</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel</t>
+        </is>
+      </c>
+      <c r="C15" s="4">
+        <v>350.0</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$/yd</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retail</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Juan</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.findglocal.com/TT/San-Juan/1797123157231816/NARS-Value-Hardware-Ltd</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reseller retail price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NARS Value Hardware</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sharp sand</t>
+        </is>
+      </c>
+      <c r="C16" s="4">
+        <v>450.0</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$/yd</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retail</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Juan</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.findglocal.com/TT/San-Juan/1797123157231816/NARS-Value-Hardware-Ltd</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retail sits 169% above the EcoEnergy base of TT$167.06 - the clearest reseller spread on record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NARS Value Hardware</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plastering sand</t>
+        </is>
+      </c>
+      <c r="C17" s="4">
+        <v>250.0</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$/yd</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retail</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Juan</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.findglocal.com/TT/San-Juan/1797123157231816/NARS-Value-Hardware-Ltd</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reseller retail price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cumosco</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel</t>
+        </is>
+      </c>
+      <c r="C18" s="4">
+        <v>300.0</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$/yd</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retail, online</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad &amp; Tobago</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.cumosco.com/product/gravel/</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Online reseller retail price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMCOL Hardware</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sharp sand</t>
+        </is>
+      </c>
+      <c r="C19" s="4">
+        <v>440.0</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$/yd</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retail</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penal</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.amcolhardwarett.com/search.php?category=Construction+Aggregate</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retail. Close to the NARS figure, which corroborates the retail band.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMCOL Hardware</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backfill / overburden</t>
+        </is>
+      </c>
+      <c r="C20" s="4">
+        <v>140.625</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$/yd3</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8-yard load at TT$1,125</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL (DELIVERED)</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Likely delivered</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penal</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.amcolhardwarett.com/search.php?category=Construction+Aggregate</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Benchmark source for backfill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMCOL Hardware</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand fill</t>
+        </is>
+      </c>
+      <c r="C21" s="4">
+        <v>126.563</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$/yd3</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-yard load at TT$1,265.63</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL (DELIVERED)</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Likely delivered</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penal</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.amcolhardwarett.com/search.php?category=Construction+Aggregate</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Benchmark source for sand fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMCOL Hardware</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/8 aggregate mix</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">NOT RETRIEVED</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n/a</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$ per load</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8-yard load TT$2,300; 10-yard mix TT$3,000</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL (DELIVERED)</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Likely delivered</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penal</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.amcolhardwarett.com/search.php?category=Construction+Aggregate</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Load pricing, grading of the mix not stated - not a like-for-like yd3 comparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On The Line General Hardware</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plastering sand</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">NOT RETRIEVED</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EX-QUARRY (STATE)</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n/a</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Guaico, Sangre Grande</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://nqcl.co.tt/wp-content/uploads/NQCL-Price-List-2025.pdf</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A public NQCL price list PDF exists but the domain is blocked by this environment's egress policy, so it was NOT retrieved. This is the highest-value missing input - it is the state benchmark.</t>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$ per load</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$1,200 per load</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL (DELIVERED)</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Load</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chaguanas / Felicity</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.equipment10.com/TT/Chaguanas/1915323488711905/On-The-Line-General-Hardware</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Load size not stated, so no yd3 rate can be derived without inventing the load volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On The Line General Hardware</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT RETRIEVED</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$ per load</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$2,350 per load</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL (DELIVERED)</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Load</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chaguanas / Felicity</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.equipment10.com/TT/Chaguanas/1915323488711905/On-The-Line-General-Hardware</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Load size not stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad Quarry Materials</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT RETRIEVED</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$ per load</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$1,800 per load</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL (DELIVERED)</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Load</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sangre Grande</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.findglocal.com/TT/Sangre-Grande-Town/106173400997686/Trinidad-Quarry-Materials</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Load size not stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad Quarry Materials</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plastering sand</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT RETRIEVED</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$ per load</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$1,400 per load</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL (DELIVERED)</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Load</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sangre Grande</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.findglocal.com/TT/Sangre-Grande-Town/106173400997686/Trinidad-Quarry-Materials</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Load size not stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pine Road, Matura</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plastering sand</t>
+        </is>
+      </c>
+      <c r="C27" s="4">
+        <v>67.5</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$/yd3</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collection</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EX-QUARRY (COLLECTION)</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collection</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matura</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior EcoEnergy workbook (merged 2026-09-12)</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recovered from prior canon. Sits BELOW the EcoEnergy plastering sand base of TT$75.94, so quote location-specific where this source competes.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K14"/>
+  <autoFilter ref="A5:K27"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -8225,7 +10795,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 1   |   12 September 2026  02:04 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 2   |   12 September 2026  02:13 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -8259,7 +10829,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">New qualified prospects this cycle</t>
+          <t xml:space="preserve">New prospects discovered this cycle</t>
         </is>
       </c>
       <c r="B6" s="3">
@@ -8267,7 +10837,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daily target is 25. Target exceeded.</t>
+          <t xml:space="preserve">Daily target is 25.</t>
         </is>
       </c>
     </row>
@@ -8306,277 +10876,285 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total prospects in pipeline</t>
+          <t xml:space="preserve">Carried forward from prior canon</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cold start: the pipeline did not exist before this cycle.</t>
+          <t xml:space="preserve">Merged from the previous EcoEnergy workbook on 2026-09-12. Not counted against the daily target.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BY PRIORITY</t>
-        </is>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duplicates avoided on merge</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Concrete Aggregate Suppliers was already held as ECO-0006 and was updated, not duplicated (section 10).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIER 1</t>
+          <t xml:space="preserve">Total prospects in pipeline</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <v>24</v>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Highest-value recurring buyers and resellers.</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C11" s="7"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TIER 2</t>
-        </is>
-      </c>
-      <c r="B12" s="3">
-        <v>15</v>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary commercial buyers.</t>
-        </is>
-      </c>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BY PRIORITY</t>
+        </is>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIER 3</t>
+          <t xml:space="preserve">TIER 1</t>
         </is>
       </c>
       <c r="B13" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low-volume but steady.</t>
+          <t xml:space="preserve">Highest-value recurring buyers and resellers.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BENCHMARK</t>
+          <t xml:space="preserve">TIER 2</t>
         </is>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Competitors and price references, not buyers.</t>
+          <t xml:space="preserve">Secondary commercial buyers.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BY SEGMENT</t>
-        </is>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 3</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <v>4</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low-volume but steady.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ready-mix and block producers</t>
+          <t xml:space="preserve">BENCHMARK</t>
         </is>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Highest continuous aggregate draw.</t>
+          <t xml:space="preserve">Competitors and price references, not buyers.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hardware stores and building-material resellers</t>
-        </is>
-      </c>
-      <c r="B17" s="3">
-        <v>13</v>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Already sell aggregate, therefore already buy it.</t>
-        </is>
-      </c>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BY SEGMENT</t>
+        </is>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contractors, civil, earthworks and drainage</t>
+          <t xml:space="preserve">Ready-mix and block producers</t>
         </is>
       </c>
       <c r="B18" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Project-driven volume.</t>
+          <t xml:space="preserve">Highest continuous aggregate draw.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">State developers and agencies</t>
+          <t xml:space="preserve">Hardware stores and building-material resellers</t>
         </is>
       </c>
       <c r="B19" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tender and vendor registration route.</t>
+          <t xml:space="preserve">Already sell aggregate, therefore already buy it.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trucking and haulage</t>
+          <t xml:space="preserve">Contractors, civil, earthworks and drainage</t>
         </is>
       </c>
       <c r="B20" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buyers and potential delivery partners.</t>
+          <t xml:space="preserve">Project-driven volume.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landscaping</t>
+          <t xml:space="preserve">State developers and agencies</t>
         </is>
       </c>
       <c r="B21" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Batch into one campaign.</t>
+          <t xml:space="preserve">Tender and vendor registration route.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COMMERCIAL ACTIVITY</t>
-        </is>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trucking and haulage</t>
+        </is>
+      </c>
+      <c r="B22" s="3">
+        <v>7</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buyers and potential delivery partners.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified direct contact details captured</t>
+          <t xml:space="preserve">Landscaping</t>
         </is>
       </c>
       <c r="B23" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLOCKED. Direct page fetches are refused by this environment's egress policy, so no telephone number, e-mail address or WhatsApp number could be verified. None were invented.</t>
+          <t xml:space="preserve">Batch into one campaign.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Outreach messages sent</t>
-        </is>
-      </c>
-      <c r="B24" s="3">
-        <v>0</v>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No messaging integration was authorised or available. Nothing recorded as sent.</t>
-        </is>
-      </c>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMERCIAL ACTIVITY</t>
+        </is>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Responses received</t>
+          <t xml:space="preserve">Prospects with a verified contact route</t>
         </is>
       </c>
       <c r="B25" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">No outreach, therefore no responses.</t>
+          <t xml:space="preserve">All carried forward from prior canon. Telephone and e-mail for these were verified previously, not by this cycle's searches.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quote requests</t>
+          <t xml:space="preserve">Prospects with NO contact route</t>
         </is>
       </c>
       <c r="B26" s="3">
-        <v>0</v>
-      </c>
-      <c r="C26" s="7"/>
+        <v>47</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sourced and named, but no number or address could be verified from this environment. None invented.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quotes issued</t>
+          <t xml:space="preserve">Outreach messages sent</t>
         </is>
       </c>
       <c r="B27" s="3">
-        <v>0</v>
-      </c>
-      <c r="C27" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cumosco and KAMCO, both by e-mail on 2026-09-12. Prior canon. This agent sent nothing.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negotiations open</t>
+          <t xml:space="preserve">Responses received</t>
         </is>
       </c>
       <c r="B28" s="3">
         <v>0</v>
       </c>
-      <c r="C28" s="7"/>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Both outbound e-mails are still pending a reply.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customers won</t>
+          <t xml:space="preserve">Quote requests</t>
         </is>
       </c>
       <c r="B29" s="3">
@@ -8585,171 +11163,234 @@
       <c r="C29" s="7"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRICING</t>
-        </is>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quotes issued</t>
+        </is>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cumosco was quoted TT$125 / 195 / 205 per yd3 on 2026-09-12.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Materials with an EcoEnergy base price</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 of 6</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3/4 gravel, 3/8 gravel, sharp sand, plastering sand.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Negotiations open</t>
+        </is>
+      </c>
+      <c r="B31" s="3">
+        <v>0</v>
+      </c>
+      <c r="C31" s="7"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Materials flagged MARKET VERIFICATION REQUIRED</t>
+          <t xml:space="preserve">Customers won</t>
         </is>
       </c>
       <c r="B32" s="3">
-        <v>2</v>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pitrun and sandfill/backfill - no published T&amp;T price found.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C32" s="7"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pricing rule applied</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Benchmark x 0.90</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10% below verified market benchmark.</t>
-        </is>
-      </c>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRICING EXCEPTION - ACTION REQUIRED</t>
+        </is>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maximum negotiated discount</t>
+          <t xml:space="preserve">Cumosco quotation above list price</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30%</t>
+          <t xml:space="preserve">CORRECTION DUE</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Closing tool. Never automatic, never advertised.</t>
+          <t xml:space="preserve">The 2026-09-12 quote of TT$125 / 195 / 205 per yd3 for pitrun / 3/8 / 3/4 sits ABOVE the canon list price of TT$77.63 / 167.06 / 167.06. Owner ruled on 2026-09-12 that the price list is canon, so a corrected quotation must be issued to Cumosco before any follow-up.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Next scheduled market review</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-13 23:59 (Sunday, Trinidad time, AST/UTC-4)</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Brief section 6.</t>
-        </is>
-      </c>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRICING</t>
+        </is>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BLOCKERS - REQUIRE HUMAN ACTION</t>
-        </is>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Materials with an EcoEnergy base price</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 of 7</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4 gravel, 3/8 gravel, sharp sand, plastering sand.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Contact detail acquisition</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BLOCKING</t>
-        </is>
+          <t xml:space="preserve">Materials flagged MARKET VERIFICATION REQUIRED</t>
+        </is>
+      </c>
+      <c r="B37" s="3">
+        <v>0</v>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Directory and company pages (findyello.com, nqcl.co.tt, energy.gov.tt and others) are refused by the egress proxy. Without them no prospect can be contacted. Allowlist those hosts, or supply the details from a machine with normal web access.</t>
+          <t xml:space="preserve">Pitrun and sandfill/backfill - no published T&amp;T price found.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Messaging integration</t>
+          <t xml:space="preserve">Pricing rule applied</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLOCKING</t>
+          <t xml:space="preserve">Benchmark x 0.90</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">No authorised e-mail or WhatsApp sending tool is connected, so outreach cannot be executed even once addresses exist.</t>
+          <t xml:space="preserve">10% below verified market benchmark.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. NQCL price list</t>
+          <t xml:space="preserve">Maximum negotiated discount</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIGH VALUE</t>
+          <t xml:space="preserve">30%</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The state price list PDF is public but blocked. It is the strongest available benchmark and would lift pricing confidence from LOW to supported.</t>
+          <t xml:space="preserve">Closing tool. Never automatic, never advertised.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Next scheduled market review</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-13 23:59 (Sunday, Trinidad time, AST/UTC-4)</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brief section 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKERS - REQUIRE HUMAN ACTION</t>
+        </is>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Contact details for the discovered prospects</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKING</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47 of 59 prospects have no verified contact route. Directory and company pages (findyello.com, nqcl.co.tt, energy.gov.tt, tt.directory) are refused by the egress proxy. Allowlist those hosts, or supply the details from a machine with ordinary web access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Messaging integration</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKING</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No authorised e-mail or messaging tool is connected to this agent. The two e-mails on record were sent outside it, through Outlook. Until an integration is authorised, outreach cannot be executed here even for the 12 prospects that do have a contact route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. NQCL price list PDF</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIALLY RESOLVED</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The pitrun benchmark of TT$86.25/yd3 was recovered from prior canon, so pitrun is now priced. The PDF itself is still blocked, and it is effective 31-Aug-2022, so the benchmark is four years old.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">4. Social comment mining</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">NOT ACCESSIBLE</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Facebook, Instagram, X and Threads are not reachable from this environment. Section 4 comment mining could not be performed beyond what public search indexes surfaced.</t>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facebook, Instagram, X and Threads are not reachable from this environment. Section 4 comment mining could not be run beyond what public search indexes surfaced.</t>
         </is>
       </c>
     </row>
@@ -8759,7 +11400,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -8767,7 +11408,8 @@
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="56" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="56" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8780,7 +11422,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 1   |   12 September 2026  02:04 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 2   |   12 September 2026  02:13 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -8820,6 +11462,11 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Origin</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Buying Signal</t>
         </is>
       </c>
@@ -8852,6 +11499,11 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Publishes a public price list; state-owned market price regulator.</t>
         </is>
       </c>
@@ -8884,6 +11536,11 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Publishes bulk aggregate pricing per cubic yard - direct price benchmark.</t>
         </is>
       </c>
@@ -8916,6 +11573,11 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Operates own sand and gravel plants feeding an internal ready-mix division.</t>
         </is>
       </c>
@@ -8948,6 +11610,11 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Described as one of the largest suppliers of aggregates to Trinidad's construction industry AND a major road contractor - consumes and resells.</t>
         </is>
       </c>
@@ -8980,6 +11647,11 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Named as an established quarry operator (est. 2000).</t>
         </is>
       </c>
@@ -9007,10 +11679,15 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aggregate wholesaler/supplier</t>
+          <t xml:space="preserve">Aggregate supplier / equipment</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Directory-listed dedicated aggregate supply business - core reseller profile.</t>
         </is>
@@ -9044,6 +11721,11 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Long-established (1976) materials producer on a large site; leading regional clay products producer.</t>
         </is>
       </c>
@@ -9076,6 +11758,11 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multi-plant national ready-mix operation - continuous high-volume sand and gravel consumption.</t>
         </is>
       </c>
@@ -9108,6 +11795,11 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Described as one of the premiere and largest readymix suppliers - multi-site.</t>
         </is>
       </c>
@@ -9140,6 +11832,11 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Directory-listed ready-mix manufacturer.</t>
         </is>
       </c>
@@ -9172,6 +11869,11 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Directory-listed ready-mix producer.</t>
         </is>
       </c>
@@ -9204,6 +11906,11 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Manufactures foundation blocks, standard/ventilation/decorative blocks and pavers - continuous sand and gravel feed.</t>
         </is>
       </c>
@@ -9236,6 +11943,11 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Established 2015 and recently made a self-sufficient subsidiary serving the development sector - growth signal.</t>
         </is>
       </c>
@@ -9268,6 +11980,11 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Largest manufacturer of clay building blocks in the English-speaking Caribbean; also retails bulk and bagged aggregate.</t>
         </is>
       </c>
@@ -9300,6 +12017,11 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Largest hardware and building-materials chain in T&amp;T; multi-branch national distribution.</t>
         </is>
       </c>
@@ -9332,6 +12054,11 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">ACTIVE PUBLIC ADVERTISEMENT: 'Sand and Gravel is available by the Truckload (Trinidad only)' - currently trading truckload aggregate.</t>
         </is>
       </c>
@@ -9364,6 +12091,11 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Stocks sand, gravel and sharp sand alongside lumber, blocks and concrete - confirmed aggregate reseller.</t>
         </is>
       </c>
@@ -9396,6 +12128,11 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Listed as supplying sand and gravel alongside paints and power tools.</t>
         </is>
       </c>
@@ -9428,6 +12165,11 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Explicitly a WHOLESALER and retailer of building materials - wholesale buying behaviour already established.</t>
         </is>
       </c>
@@ -9460,6 +12202,11 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Operates an online hardware storefront - materials-focused business with e-commerce reach.</t>
         </is>
       </c>
@@ -9492,6 +12239,11 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Currently stocks and resells Bestcrete Aggre GO! bagged sharp sand - confirmed aggregate reseller buying from a competing quarry.</t>
         </is>
       </c>
@@ -9524,6 +12276,11 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Directory-listed top hardware store in a high-construction central corridor.</t>
         </is>
       </c>
@@ -9556,6 +12313,11 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Supplies all building material 'from foundation to finish' - foundation stage implies fill and aggregate.</t>
         </is>
       </c>
@@ -9588,6 +12350,11 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Described as Tobago's leading hardware, stocking construction materials for homeowners and contractors.</t>
         </is>
       </c>
@@ -9620,6 +12387,11 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Trading since February 2007, serving customers throughout Trinidad and Tobago.</t>
         </is>
       </c>
@@ -9652,6 +12424,11 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Three-generation family business holding extensive hardware stock.</t>
         </is>
       </c>
@@ -9684,6 +12461,11 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Roadworks, asphalting, bridges, sea defence and precast concrete - all heavy aggregate consumers.</t>
         </is>
       </c>
@@ -9716,6 +12498,11 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Over 30 years in full-service ground construction works - paving contractors consume base aggregate continuously.</t>
         </is>
       </c>
@@ -9748,6 +12535,11 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Listed among the top civil construction companies in T&amp;T by revenue (cited at USD 17.1M).</t>
         </is>
       </c>
@@ -9780,6 +12572,11 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">General contractor providing engineering and construction services nationally.</t>
         </is>
       </c>
@@ -9812,6 +12609,11 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Long-established (1933) transport and contracting business, now a large civil operation.</t>
         </is>
       </c>
@@ -9844,6 +12646,11 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Described as a leading emerging business in demolition and earth works.</t>
         </is>
       </c>
@@ -9876,6 +12683,11 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Offers drainage solutions, retaining walls and bridges - all aggregate-intensive.</t>
         </is>
       </c>
@@ -9908,6 +12720,11 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Runs an aggressive national construction programme across Infill Lots, Joint Venture and Urban Housing components.</t>
         </is>
       </c>
@@ -9940,6 +12757,11 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">HDC subsidiary (est. 2022) handling contractor procurement and construction management for residential programmes.</t>
         </is>
       </c>
@@ -9972,6 +12794,11 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Manages drainage, flood control, reclamation, highway and transportation projects - the largest aggregate-consuming programmes in the country.</t>
         </is>
       </c>
@@ -10004,6 +12831,11 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">State-owned development company (formed 1994) delivering major public building projects.</t>
         </is>
       </c>
@@ -10036,6 +12868,11 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Listed as the highest-revenue civil construction entity in T&amp;T (cited at USD 60.8M).</t>
         </is>
       </c>
@@ -10068,6 +12905,11 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Explicitly offers AGGREGATE SUPPLY alongside heavy equipment rental and transport - they resell aggregate they must buy in.</t>
         </is>
       </c>
@@ -10100,6 +12942,11 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Transports bulk and construction materials with a modern fleet; also performs construction and civil works.</t>
         </is>
       </c>
@@ -10132,6 +12979,11 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">24/7 national transport of construction materials with a certified fleet.</t>
         </is>
       </c>
@@ -10164,6 +13016,11 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Established 2002, providing haulage and storage across T&amp;T and the wider Caribbean.</t>
         </is>
       </c>
@@ -10196,6 +13053,11 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Operating since 1960 in transport services.</t>
         </is>
       </c>
@@ -10228,6 +13090,11 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Founded 2006; landscape design, CONSTRUCTION and maintenance - construction work consumes sand and gravel.</t>
         </is>
       </c>
@@ -10260,6 +13127,11 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Over 13 years operating across Trinidad, including irrigation and garden construction.</t>
         </is>
       </c>
@@ -10292,6 +13164,11 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Professional landscaping for homes and businesses including installation work.</t>
         </is>
       </c>
@@ -10324,6 +13201,11 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Trading since 2007 and has expanded beyond lawn care into broader services.</t>
         </is>
       </c>
@@ -10356,44 +13238,466 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">LIVE LISTING advertising sand, gravel and aggregates with nationwide delivery and a WhatsApp contact - an active reseller placing material now.</t>
         </is>
       </c>
     </row>
-    <row r="54"/>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0049</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On The Line General Hardware</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merged from prior canon</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advertises plastering sand and gravel by the load - an active aggregate reseller.</t>
+        </is>
+      </c>
+    </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added this cycle</t>
-        </is>
-      </c>
-      <c r="B55" s="3">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0050</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NARS Value Hardware</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merged from prior canon</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publishes per-yard retail prices across three EcoEnergy lines - a confirmed reseller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0051</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad Quarry Materials</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate reseller / delivery</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merged from prior canon</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sells gravel, plastering sand, backfill and crusher run by the load with delivery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0052</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMCOL Hardware</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merged from prior canon</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publishes an online construction aggregate catalogue including mixes, backfill and sandfill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0053</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cumosco</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Online hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merged from prior canon</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sells gravel online at TT$300/yd. Already contacted by EcoEnergy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0054</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KAMCO Marketing &amp; Contracting</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procurement / contractor</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merged from prior canon</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Construction materials procurement business. Already contacted by EcoEnergy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0055</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Southern Aggregate and Supplies Ltd</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merged from prior canon</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named as an aggregate and building materials supplier - buys aggregate to resell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0056</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">James Transport</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate supplier / trucking</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merged from prior canon</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Combines aggregate supply with transport - both a buyer and a delivery partner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0057</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gibson's Hardware</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials supplier</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merged from prior canon</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials supplier in south Trinidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0058</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K&amp;S Hardware and Plumbing Supplies</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials store</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merged from prior canon</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials store in the central construction corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0059</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seupersad's Y Junction Hardware</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials supplier</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merged from prior canon</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building materials supplier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="B66" s="3">
         <v>48</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merged from prior canon</t>
+        </is>
+      </c>
+      <c r="B67" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Weekly target</t>
         </is>
       </c>
-      <c r="B56" s="3">
+      <c r="B68" s="3">
         <v>175</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Against weekly target</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Against weekly target (discovered only)</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">27%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F57"/>
+  <autoFilter ref="A5:G69"/>
 </worksheet>
 </file>
--- a/ecoenergy/EcoEnergy_Aggregate_Sales_Pipeline.xlsx
+++ b/ecoenergy/EcoEnergy_Aggregate_Sales_Pipeline.xlsx
@@ -130,7 +130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AD64"/>
+  <dimension ref="A1:AD90"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -175,7 +175,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 2   |   12 September 2026  02:13 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 3   |   12 September 2026  04:32 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="AD7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANCHOR BENCHMARK - the only source in this cycle carrying published TTD prices for all four of EcoEnergy's core comparables. Acquired its Matura sand and gravel quarry in 2018. Part of ANSA McAL group via Abel Building Solutions.</t>
+          <t xml:space="preserve">ANCHOR BENCHMARK - the only source in this cycle carrying published TTD prices for all four of EcoEnergy's core comparables. Acquired its Matura sand and gravel quarry in 2018. Part of ANSA McAL group via Abel Building Solutions. | CYCLE 2 UPDATE (2026-09-12): Licensed quarry confirmed at the Melajo Forest Reserve, Matura. Named in the Ministry of Energy list of licensed quarry operations reported by Trinidad Express. Confirms licensed producer status.</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="AD19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same group as Bestcrete Aggregate Ltd - self-supplied, so not a buyer. Retained because it sets the published retail/bulk benchmark EcoEnergy prices against.</t>
+          <t xml:space="preserve">Same group as Bestcrete Aggregate Ltd - self-supplied, so not a buyer. Retained because it sets the published retail/bulk benchmark EcoEnergy prices against. | CYCLE 2 UPDATE (2026-09-12): Group licensed quarry confirmed at Depot Road, Longdenville (listed as ANSA McAL Limited). Named in the Ministry of Energy list of licensed quarry operations reported by Trinidad Express. Confirms licensed producer status.</t>
         </is>
       </c>
     </row>
@@ -4550,12 +4550,12 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Earthworks / civil contractor</t>
+          <t xml:space="preserve">Earthworks contractor + LICENSED QUARRY OPERATOR</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIER 1</t>
+          <t xml:space="preserve">BENCHMARK</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="AD36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Own transport fleet means they may collect ex-quarry, which improves EcoEnergy's margin. Contractor profile - aggregate is a project input. Volume is lumpy and project-driven, so qualify on current project pipeline, not on history.</t>
+          <t xml:space="preserve">Own transport fleet means they may collect ex-quarry, which improves EcoEnergy's margin. Contractor profile - aggregate is a project input. Volume is lumpy and project-driven, so qualify on current project pipeline, not on history. | CYCLE 2 UPDATE (2026-09-12): MATERIAL PROFILE CHANGE. Seereeram Brothers holds a licensed quarry at Cangrejal Road, Santa Cruz. They are a PRODUCER, not just a consumer, so the wholesale pitch is wrong for them. Reclassified from TIER 1 to BENCHMARK. Approach only for overflow or swap supply. Named in the Ministry of Energy list of licensed quarry operations reported by Trinidad Express. Confirms licensed producer status.</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING VERIFICATION</t>
+          <t xml:space="preserve">https://www.facebook.com/onthelinehardware</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="AD54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Wholesale/repeat reseller supply</t>
+          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Wholesale/repeat reseller supply | CYCLE 2 UPDATE (2026-09-12): Facebook business page located at facebook.com/onthelinehardware.</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aggregate; gravel/sand mixes; backfill; sandfill</t>
+          <t xml:space="preserve">Aggregate; gravel/sand mixes; backfill; sandfill; crusher run / blue metal (8-yard loads, M3, bagged); ballast (1/2 x 1/2 gravel with sharp sand, 10 and 11 yard loads)</t>
         </is>
       </c>
       <c r="U57" s="7" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="W57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/8 mix 8yd TT$2,300; 10yd aggregate mix TT$3,000; sharp sand TT$440/yd</t>
+          <t xml:space="preserve">3/8 mix 8yd TT$2,300; 10yd aggregate mix TT$3,000; sharp sand TT$440/yd; backfill 8yd TT$1,125; sandfill 10yd TT$1,265.63</t>
         </is>
       </c>
       <c r="X57" s="7" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="AD57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Strong reseller prospect</t>
+          <t xml:space="preserve">CARRIED FORWARD FROM PRIOR CANON. Contact details below were verified in the prior workbook and are NOT the product of this cycle's searches.  EcoEnergy opportunity as previously assessed: Strong reseller prospect | CYCLE 2 UPDATE (2026-09-12): Online catalogue carries a wider aggregate range than first recorded: crusher run and blue metal by the 8-yard load, by cubic metre and bagged, plus ballast in 10 and 11 yard loads. Their catalogue is a standing benchmark source.</t>
         </is>
       </c>
     </row>
@@ -8687,8 +8687,3856 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0060</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Class Gravel &amp; Aggregates</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate reseller</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Constance Street, Montrose, Chaguanas</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(868) 478-4400</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TNT Yellow directory (via web search)</t>
+        </is>
+      </c>
+      <c r="Q65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tntyellow.com/company/11461/A_Class_Gravel_Aggregates</t>
+        </is>
+      </c>
+      <c r="R65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A dedicated gravel and aggregate business, so it must buy from a quarry.</t>
+        </is>
+      </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; plastering sand; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="T65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel; aggregates</t>
+        </is>
+      </c>
+      <c r="U65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm on contact</t>
+        </is>
+      </c>
+      <c r="V65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="W65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTACT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA65" s="7"/>
+      <c r="AB65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telephone and open the wholesale supply conversation. Contact route is live. Pure aggregate business, so lead straight to wholesale pricing.</t>
+        </is>
+      </c>
+      <c r="AD65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). STRONGEST NEW FIT THIS CYCLE. Dedicated aggregate trader with a published telephone number. RESELLER TARGET - already sells aggregate, therefore already buys it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0061</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roopnarine Hardware Limited</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chaguanas</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.facebook.com/roopnarinehardware/</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facebook business page (via web search)</t>
+        </is>
+      </c>
+      <c r="Q66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.facebook.com/roopnarinehardware/</t>
+        </is>
+      </c>
+      <c r="R66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACTIVE ADVERTISEMENT: 'Gravel, Sharp Sand, Red Sand. Delivery available.' Currently trading aggregate.</t>
+        </is>
+      </c>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; plastering sand; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="T66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel; sharp sand; red sand; general hardware</t>
+        </is>
+      </c>
+      <c r="U66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm on contact</t>
+        </is>
+      </c>
+      <c r="V66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="W66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA66" s="7"/>
+      <c r="AB66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list. They advertise three sand and gravel lines with delivery, so the range fits directly.</t>
+        </is>
+      </c>
+      <c r="AD66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). Established 1956 and described as a leading T&amp;T hardware. RESELLER TARGET - already sells aggregate, therefore already buys it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0062</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B Chadee &amp; Sons Stockpile and Hardware Supplies Ltd</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stockpile operator / hardware</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Horquetta</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.facebook.com/BChadeeandSonsLtd</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facebook business page (via web search)</t>
+        </is>
+      </c>
+      <c r="Q67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.facebook.com/BChadeeandSonsLtd</t>
+        </is>
+      </c>
+      <c r="R67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operates a STOCKPILE segregating material grades and maintaining steady supply, with a rental and aggregate division.</t>
+        </is>
+      </c>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; plastering sand; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="T67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate (graded from stockpile); hardware tools; equipment rental</t>
+        </is>
+      </c>
+      <c r="U67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm on contact</t>
+        </is>
+      </c>
+      <c r="V67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="W67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA67" s="7"/>
+      <c r="AB67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list. Stockpile operators buy in bulk and hold inventory, which is the ideal recurring wholesale profile.</t>
+        </is>
+      </c>
+      <c r="AD67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). Stockpile operators are named explicitly in section 2 as a Tier 1 target. They run a stockpile to segregate grades and keep steady supply, and deliver nationwide at cost. RESELLER TARGET - already sells aggregate, therefore already buys it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0063</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Northeastern Hardware Ltd</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sangre Grande Town</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.facebook.com/northeasternhardwareltd/</t>
+        </is>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facebook business page (via web search)</t>
+        </is>
+      </c>
+      <c r="Q68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.facebook.com/northeasternhardwareltd/</t>
+        </is>
+      </c>
+      <c r="R68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware business in Sangre Grande, close to the Guaico and Matura quarry belt.</t>
+        </is>
+      </c>
+      <c r="S68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; plastering sand; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="T68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">General hardware</t>
+        </is>
+      </c>
+      <c r="U68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm on contact</t>
+        </is>
+      </c>
+      <c r="V68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="W68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA68" s="7"/>
+      <c r="AB68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list.</t>
+        </is>
+      </c>
+      <c r="AD68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). Northeast location sits near the quarry belt, so haulage is short. RESELLER TARGET - already sells aggregate, therefore already buys it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0064</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C.J. Lumber Ltd</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumber / building materials</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Longdenville, Chaguanas</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TNT Yellow directory (via web search)</t>
+        </is>
+      </c>
+      <c r="Q69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tntyellow.com/company/11461/A_Class_Gravel_Aggregates</t>
+        </is>
+      </c>
+      <c r="R69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Established building materials supplier in the central construction corridor.</t>
+        </is>
+      </c>
+      <c r="S69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; plastering sand; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="T69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumber; building materials</t>
+        </is>
+      </c>
+      <c r="U69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm on contact</t>
+        </is>
+      </c>
+      <c r="V69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="W69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA69" s="7"/>
+      <c r="AB69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list.</t>
+        </is>
+      </c>
+      <c r="AD69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). Established 1997. RESELLER TARGET - already sells aggregate, therefore already buys it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0065</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samlal Seepersad Hardware Limited</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / building supplies</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TNT Island directory (via web search)</t>
+        </is>
+      </c>
+      <c r="Q70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http://www.tntisland.com/hardwarestores.html</t>
+        </is>
+      </c>
+      <c r="R70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplying building materials nationally for over 50 years.</t>
+        </is>
+      </c>
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; plastering sand; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="T70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building supplies</t>
+        </is>
+      </c>
+      <c r="U70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm on contact</t>
+        </is>
+      </c>
+      <c r="V70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="W70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA70" s="7"/>
+      <c r="AB70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list.</t>
+        </is>
+      </c>
+      <c r="AD70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). RESELLER TARGET - already sells aggregate, therefore already buys it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0066</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Island Roofing &amp; Hardware Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / roofing</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TNT Island directory (via web search)</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http://www.tntisland.com/hardwarestores.html</t>
+        </is>
+      </c>
+      <c r="R71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies lumber, roofing materials and general hardware.</t>
+        </is>
+      </c>
+      <c r="S71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; plastering sand; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="T71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumber; roofing; hardware</t>
+        </is>
+      </c>
+      <c r="U71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm on contact</t>
+        </is>
+      </c>
+      <c r="V71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="W71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA71" s="7"/>
+      <c r="AB71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list.</t>
+        </is>
+      </c>
+      <c r="AD71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). RESELLER TARGET - already sells aggregate, therefore already buys it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0067</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aqucan Hardware and Construction Ltd</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware + construction</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TNT Island directory (via web search)</t>
+        </is>
+      </c>
+      <c r="Q72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http://www.tntisland.com/hardwarestores.html</t>
+        </is>
+      </c>
+      <c r="R72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies construction tools and accessories and carries out construction work, so it both buys and uses material.</t>
+        </is>
+      </c>
+      <c r="S72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; plastering sand; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="T72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Household, garden and construction tools and accessories</t>
+        </is>
+      </c>
+      <c r="U72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm on contact</t>
+        </is>
+      </c>
+      <c r="V72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="W72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA72" s="7"/>
+      <c r="AB72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list. Dual profile, so qualify for both resale and site consumption.</t>
+        </is>
+      </c>
+      <c r="AD72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). RESELLER TARGET - already sells aggregate, therefore already buys it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0068</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discount Hardware And Building Supplies</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / building supplies</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FindYello directory (via web search)</t>
+        </is>
+      </c>
+      <c r="Q73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.findyello.com/trinidad/discount-hardware-and-building-supplies/</t>
+        </is>
+      </c>
+      <c r="R73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discount building supplies business, so it competes on price and is sensitive to purchase cost.</t>
+        </is>
+      </c>
+      <c r="S73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; plastering sand; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="T73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building supplies</t>
+        </is>
+      </c>
+      <c r="U73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm on contact</t>
+        </is>
+      </c>
+      <c r="V73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="W73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA73" s="7"/>
+      <c r="AB73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list. A discounter lives on purchase price, which is exactly EcoEnergy's lever.</t>
+        </is>
+      </c>
+      <c r="AD73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). RESELLER TARGET - already sells aggregate, therefore already buys it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0069</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sands Parry</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand and gravel supplier</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FindYello directory (via web search)</t>
+        </is>
+      </c>
+      <c r="Q74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.findyello.com/Trinidad/Sands-Parry/</t>
+        </is>
+      </c>
+      <c r="R74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed under sand and gravel in a national directory.</t>
+        </is>
+      </c>
+      <c r="S74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; plastering sand; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="T74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand; gravel</t>
+        </is>
+      </c>
+      <c r="U74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm on contact</t>
+        </is>
+      </c>
+      <c r="V74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="W74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA74" s="7"/>
+      <c r="AB74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list. Confirm trading status and exact business name before any approach.</t>
+        </is>
+      </c>
+      <c r="AD74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). Thin record. Directory listing only, and the name may be a directory rendering rather than the registered trading name. Verify before spending effort. RESELLER TARGET - already sells aggregate, therefore already buys it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0070</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinity Readymix Limited</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ready-mix concrete producer</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penal and Point Lisas</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://trinityreadymix.com/</t>
+        </is>
+      </c>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Web Search</t>
+        </is>
+      </c>
+      <c r="Q75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://trinityreadymix.com/</t>
+        </is>
+      </c>
+      <c r="R75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two batching plants, at Penal and Point Lisas, so sand and gravel draw is continuous.</t>
+        </is>
+      </c>
+      <c r="S75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sharp sand; 3/8 gravel; 3/4 gravel</t>
+        </is>
+      </c>
+      <c r="T75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ready-mixed concrete</t>
+        </is>
+      </c>
+      <c r="U75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST HIGH (inferred from two plants) - to confirm</t>
+        </is>
+      </c>
+      <c r="V75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST continuous (inferred) - to confirm</t>
+        </is>
+      </c>
+      <c r="W75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA75" s="7"/>
+      <c r="AB75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list. Point Lisas sits in the heaviest industrial corridor in the country.</t>
+        </is>
+      </c>
+      <c r="AD75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). Not previously held. Ready-mix plants are the highest continuous aggregate draw in the market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0071</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Central Concrete Product Ltd</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Precast concrete manufacturer</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://centralconcretett.com/</t>
+        </is>
+      </c>
+      <c r="P76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Web Search</t>
+        </is>
+      </c>
+      <c r="Q76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://centralconcretett.com/</t>
+        </is>
+      </c>
+      <c r="R76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Market leader in precast concrete products, incorporated 1976. Precast production consumes graded aggregate continuously.</t>
+        </is>
+      </c>
+      <c r="S76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sharp sand; 3/8 gravel; 3/4 gravel</t>
+        </is>
+      </c>
+      <c r="T76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Precast concrete products</t>
+        </is>
+      </c>
+      <c r="U76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST HIGH (inferred from precast scale) - to confirm</t>
+        </is>
+      </c>
+      <c r="V76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST continuous (inferred) - to confirm</t>
+        </is>
+      </c>
+      <c r="W76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA76" s="7"/>
+      <c r="AB76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list.</t>
+        </is>
+      </c>
+      <c r="AD76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). Precast is a steady, quality-sensitive aggregate buyer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0072</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRESTCON 2021 Limited</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Precast / prestressed concrete</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.prestcon2021.com/</t>
+        </is>
+      </c>
+      <c r="P77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Web Search</t>
+        </is>
+      </c>
+      <c r="Q77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.prestcon2021.com/</t>
+        </is>
+      </c>
+      <c r="R77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manufactures precast and prestressed products for bridges, docks, jetties, marinas and petrochemical structures.</t>
+        </is>
+      </c>
+      <c r="S77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sharp sand; 3/8 gravel; 3/4 gravel</t>
+        </is>
+      </c>
+      <c r="T77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Precast and prestressed concrete products</t>
+        </is>
+      </c>
+      <c r="U77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST MEDIUM-HIGH (inferred) - to confirm</t>
+        </is>
+      </c>
+      <c r="V77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST project-driven</t>
+        </is>
+      </c>
+      <c r="W77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA77" s="7"/>
+      <c r="AB77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list. Prestressed work demands consistent high-spec aggregate, so quality is the lead, not price.</t>
+        </is>
+      </c>
+      <c r="AD77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). Serves the Caribbean and northeastern South America, so volumes may exceed the domestic picture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0073</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">General Earth Movers Limited (GEML)</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphalt / civil contractor</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://gemlttwi.com/</t>
+        </is>
+      </c>
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Web Search</t>
+        </is>
+      </c>
+      <c r="Q78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://gemlttwi.com/asphalt/</t>
+        </is>
+      </c>
+      <c r="R78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Produces hot mix asphalt from a wide range of aggregate combinations, and performs milling and paving at scale.</t>
+        </is>
+      </c>
+      <c r="S78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/4 gravel; 3/8 gravel; sharp sand</t>
+        </is>
+      </c>
+      <c r="T78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hot mix asphalt; civil construction</t>
+        </is>
+      </c>
+      <c r="U78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST HIGH (inferred from asphalt production) - to confirm</t>
+        </is>
+      </c>
+      <c r="V78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST project-driven</t>
+        </is>
+      </c>
+      <c r="W78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA78" s="7"/>
+      <c r="AB78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list. An asphalt plant buys graded aggregate by the thousand tonnes. Lead with consistent grading.</t>
+        </is>
+      </c>
+      <c r="AD78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). In construction since 1945 and producing asphalt since 2000. Asphalt producers are among the largest aggregate consumers in any market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0074</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Danny's Enterprises Company Limited (DECL)</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roadworks / drainage contractor</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.decltt.com/</t>
+        </is>
+      </c>
+      <c r="P79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Web Search</t>
+        </is>
+      </c>
+      <c r="Q79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.decltt.com/</t>
+        </is>
+      </c>
+      <c r="R79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roadworks, asphalt paving and installation of wick and earthquake drains, all aggregate-intensive.</t>
+        </is>
+      </c>
+      <c r="S79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/4 gravel; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="T79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roadworks; asphalt paving; drainage installation</t>
+        </is>
+      </c>
+      <c r="U79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST MEDIUM-HIGH (inferred) - to confirm</t>
+        </is>
+      </c>
+      <c r="V79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST project-driven</t>
+        </is>
+      </c>
+      <c r="W79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA79" s="7"/>
+      <c r="AB79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list. Drainage installation consumes graded gravel and backfill steadily.</t>
+        </is>
+      </c>
+      <c r="AD79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). Drainage work is a strong fit for the backfill and sandfill lines now priced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0075</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lake Asphalt of Trinidad and Tobago (1978) Limited</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State asphalt producer</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brighton, La Brea</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wikipedia / web search</t>
+        </is>
+      </c>
+      <c r="Q80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://en.wikipedia.org/wiki/Lake_Asphalt_of_Trinidad_and_Tobago</t>
+        </is>
+      </c>
+      <c r="R80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State asphalt producer. Asphalt manufacture requires aggregate blending.</t>
+        </is>
+      </c>
+      <c r="S80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/8 gravel; 3/4 gravel; sharp sand</t>
+        </is>
+      </c>
+      <c r="T80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphalt and asphalt products</t>
+        </is>
+      </c>
+      <c r="U80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST MEDIUM (inferred) - to confirm</t>
+        </is>
+      </c>
+      <c r="V80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST recurring</t>
+        </is>
+      </c>
+      <c r="W80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA80" s="7"/>
+      <c r="AB80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identify the procurement route. State entity, so expect vendor registration and tender.</t>
+        </is>
+      </c>
+      <c r="AD80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). State entity. Long lead time through formal procurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0076</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphalt Paving Co Ltd</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphalt paving contractor</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FindYello directory (via web search)</t>
+        </is>
+      </c>
+      <c r="Q81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.findyello.com/trinidad/Asphalt-Paving-Co-Ltd/</t>
+        </is>
+      </c>
+      <c r="R81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Directory-listed asphalt paving contractor.</t>
+        </is>
+      </c>
+      <c r="S81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/4 gravel; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="T81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphalt paving</t>
+        </is>
+      </c>
+      <c r="U81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm on contact</t>
+        </is>
+      </c>
+      <c r="V81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="W81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA81" s="7"/>
+      <c r="AB81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list.</t>
+        </is>
+      </c>
+      <c r="AD81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). Paving contractors buy road base and pitrun in volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0077</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad Asphalt Pavers General Contractors Ltd</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphalt / general contractor</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FindYello directory (via web search)</t>
+        </is>
+      </c>
+      <c r="Q82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.findyello.com/trinidad/trinidad-asphalt-pavers-general-contractors-ltd/ksort:t/</t>
+        </is>
+      </c>
+      <c r="R82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Directory-listed asphalt and general contracting firm.</t>
+        </is>
+      </c>
+      <c r="S82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/4 gravel; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="T82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphalt paving; general contracting</t>
+        </is>
+      </c>
+      <c r="U82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm on contact</t>
+        </is>
+      </c>
+      <c r="V82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="W82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA82" s="7"/>
+      <c r="AB82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify direct contact from the source, then issue the wholesale introduction and price list.</t>
+        </is>
+      </c>
+      <c r="AD82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). Confirm this is distinct from Carib Asphalt Pavers (ECO-0030) before approach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0078</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weathershield Systems Caribbean Limited</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphalt / waterproofing contractor</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 3</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FindYello directory (via web search)</t>
+        </is>
+      </c>
+      <c r="Q83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.findyello.com/trinidad/Asphalt-Paving-Co-Ltd/</t>
+        </is>
+      </c>
+      <c r="R83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Founded 1994, successor to Trinidad Mastic Asphalt &amp; Contracting Company.</t>
+        </is>
+      </c>
+      <c r="S83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sharp sand; 3/8 gravel</t>
+        </is>
+      </c>
+      <c r="T83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mastic asphalt; waterproofing systems</t>
+        </is>
+      </c>
+      <c r="U83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm on contact</t>
+        </is>
+      </c>
+      <c r="V83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="W83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA83" s="7"/>
+      <c r="AB83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low priority. Qualify material need by telephone before any commercial effort.</t>
+        </is>
+      </c>
+      <c r="AD83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). Mastic asphalt and waterproofing use far less bulk aggregate than roadbuilding. Weak fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0079</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mineral Mines of Trinidad Limited</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licensed quarry operator</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENCHMARK</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vega de Oropouche</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad Express (via web search)</t>
+        </is>
+      </c>
+      <c r="Q84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://trinidadexpress.com/news/local/stop-quarrying-mashing-up-our-lives/article_74ce0d92-1b6d-11ed-a7db-f3a68b15cf27.html</t>
+        </is>
+      </c>
+      <c r="R84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holds a licence to mine or process aggregate.</t>
+        </is>
+      </c>
+      <c r="S84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - producer</t>
+        </is>
+      </c>
+      <c r="T84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quarry aggregate</t>
+        </is>
+      </c>
+      <c r="U84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - producer</t>
+        </is>
+      </c>
+      <c r="V84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - producer</t>
+        </is>
+      </c>
+      <c r="W84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA84" s="7"/>
+      <c r="AB84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monitor pricing. Approach only for overflow or swap supply.</t>
+        </is>
+      </c>
+      <c r="AD84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). LICENSED QUARRY OPERATOR. Competitor and benchmark, not a wholesale buyer. Track pricing and treat as a possible overflow or swap counterparty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0080</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estate Management and Business Development Company Limited (EMBD)</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State land company / licensed quarry</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENCHMARK</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coco Road, Claxton Bay and Milton Village, Couva</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad Express (via web search)</t>
+        </is>
+      </c>
+      <c r="Q85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://trinidadexpress.com/news/local/stop-quarrying-mashing-up-our-lives/article_74ce0d92-1b6d-11ed-a7db-f3a68b15cf27.html</t>
+        </is>
+      </c>
+      <c r="R85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holds licensed quarry operations at two sites.</t>
+        </is>
+      </c>
+      <c r="S85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - producer</t>
+        </is>
+      </c>
+      <c r="T85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quarry aggregate</t>
+        </is>
+      </c>
+      <c r="U85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - producer</t>
+        </is>
+      </c>
+      <c r="V85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - producer</t>
+        </is>
+      </c>
+      <c r="W85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA85" s="7"/>
+      <c r="AB85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monitor. State entity holding two licensed sites, so also a possible supply partner.</t>
+        </is>
+      </c>
+      <c r="AD85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). LICENSED QUARRY OPERATOR. Competitor and benchmark, not a wholesale buyer. Track pricing and treat as a possible overflow or swap counterparty. State-owned land development company, so its quarrying is secondary to its main business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0081</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AADS Multi-Tasking Limited</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licensed quarry operator</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENCHMARK</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rio Grande Trace, Matura</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad Express (via web search)</t>
+        </is>
+      </c>
+      <c r="Q86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://trinidadexpress.com/news/local/stop-quarrying-mashing-up-our-lives/article_74ce0d92-1b6d-11ed-a7db-f3a68b15cf27.html</t>
+        </is>
+      </c>
+      <c r="R86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holds a licence to mine or process aggregate.</t>
+        </is>
+      </c>
+      <c r="S86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - producer</t>
+        </is>
+      </c>
+      <c r="T86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quarry aggregate</t>
+        </is>
+      </c>
+      <c r="U86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - producer</t>
+        </is>
+      </c>
+      <c r="V86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - producer</t>
+        </is>
+      </c>
+      <c r="W86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA86" s="7"/>
+      <c r="AB86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monitor pricing. Matura site, so same catchment as Bestcrete.</t>
+        </is>
+      </c>
+      <c r="AD86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). LICENSED QUARRY OPERATOR. Competitor and benchmark, not a wholesale buyer. Track pricing and treat as a possible overflow or swap counterparty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0082</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Firma Fabrication and Construction Limited</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licensed quarry operator + contractor</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 3</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Melajo Forest Reserve, Sangre Grande</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad Express (via web search)</t>
+        </is>
+      </c>
+      <c r="Q87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://trinidadexpress.com/news/local/stop-quarrying-mashing-up-our-lives/article_74ce0d92-1b6d-11ed-a7db-f3a68b15cf27.html</t>
+        </is>
+      </c>
+      <c r="R87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holds a licensed quarry and also carries out fabrication and construction.</t>
+        </is>
+      </c>
+      <c r="S87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Possible overflow purchaser during construction works</t>
+        </is>
+      </c>
+      <c r="T87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quarry aggregate; fabrication; construction</t>
+        </is>
+      </c>
+      <c r="U87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown - to establish</t>
+        </is>
+      </c>
+      <c r="V87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown - to establish</t>
+        </is>
+      </c>
+      <c r="W87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA87" s="7"/>
+      <c r="AB87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qualify carefully. They produce their own aggregate, so only their construction arm could buy.</t>
+        </is>
+      </c>
+      <c r="AD87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). LICENSED QUARRY OPERATOR. Competitor and benchmark, not a wholesale buyer. Track pricing and treat as a possible overflow or swap counterparty. Dual profile, so the construction side may still buy grades they do not produce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0083</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conveyor and Plant Solutions</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant and conveyor supplier</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 3</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lot 54 Cemetery Street, Balmain, Couva</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T&amp;T Manufacturers Association directory (via web search)</t>
+        </is>
+      </c>
+      <c r="Q88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http://ttmanufacturers.memberzone.com/list/ql/manufacturing-production-wholesale-16</t>
+        </is>
+      </c>
+      <c r="R88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies conveyor and plant equipment to the quarry and materials sector.</t>
+        </is>
+      </c>
+      <c r="S88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unlikely direct buyer - route to their quarry clients</t>
+        </is>
+      </c>
+      <c r="T88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conveyor and plant equipment</t>
+        </is>
+      </c>
+      <c r="U88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="V88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="W88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA88" s="7"/>
+      <c r="AB88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Treat as a referral channel rather than a buyer. Their clients are quarry and aggregate operators.</t>
+        </is>
+      </c>
+      <c r="AD88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). CHANNEL PARTNER, not a prospect in the usual sense. Equipment suppliers know every operator in the sector and their introductions carry weight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0084</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Christle Limited</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial supplier</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 3</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lot 18E O'Meara Industrial Estate, Arima</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(868) 235-5312</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T&amp;T Manufacturers Association directory (via web search)</t>
+        </is>
+      </c>
+      <c r="Q89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http://ttmanufacturers.memberzone.com/list/ql/manufacturing-production-wholesale-16</t>
+        </is>
+      </c>
+      <c r="R89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed in the manufacturers association wholesale directory with a published telephone number.</t>
+        </is>
+      </c>
+      <c r="S89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish on contact</t>
+        </is>
+      </c>
+      <c r="T89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not established</t>
+        </is>
+      </c>
+      <c r="U89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
+        </is>
+      </c>
+      <c r="V89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
+        </is>
+      </c>
+      <c r="W89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTACT AVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA89" s="7"/>
+      <c r="AB89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telephone to establish what they actually trade before any commercial effort.</t>
+        </is>
+      </c>
+      <c r="AD89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). Contact route is live but the line of business is NOT established. Qualify first. Recorded because the telephone number is published and verification is cheap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0085</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad and Tobago Aggregate Producers Alliance (TTAPA)</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industry association</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENCHMARK</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad Guardian (via web search)</t>
+        </is>
+      </c>
+      <c r="Q90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.guardian.co.tt/news/24-quarries-on-strike-operators-demand-processing-licences-amid-govt-scrutiny-6.2.2442975.5bea92b6d7</t>
+        </is>
+      </c>
+      <c r="R90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newly formed alliance representing aggregate producers. Led the November 2025 shutdown of 24 quarries over processing licences.</t>
+        </is>
+      </c>
+      <c r="S90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="T90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - industry body</t>
+        </is>
+      </c>
+      <c r="U90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="V90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="W90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="X90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Y90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="Z90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AA90" s="7"/>
+      <c r="AB90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Establish whether EcoEnergy is or should be a member. Membership gives licensing intelligence and direct access to every producer in the sector.</t>
+        </is>
+      </c>
+      <c r="AD90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 2 (2026-09-12). STRATEGIC CONTACT, not a buyer. TTAPA is the centre of the licensing dispute driving the current supply disruption. Whoever sits inside it sees the shortage coming first.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:AD64"/>
+  <autoFilter ref="A5:AD90"/>
 </worksheet>
 </file>
 
@@ -8724,7 +12572,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 2   |   12 September 2026  02:13 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 3   |   12 September 2026  04:32 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -8991,7 +12839,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 2   |   12 September 2026  02:13 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 3   |   12 September 2026  04:32 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -9453,7 +13301,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -9479,7 +13327,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 2   |   12 September 2026  02:13 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 3   |   12 September 2026  04:32 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -10770,14 +14618,238 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facebook Marketplace seller (T&amp;T)</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel</t>
+        </is>
+      </c>
+      <c r="C28" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$/yd</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retail, delivered</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL (DELIVERED)</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delivery</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.facebook.com/marketplace/116087261735365/gravel/</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cycle 2 observation. Same listing also offers TT$60 per 75lb bag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facebook Marketplace seller (T&amp;T)</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gravel - bagged 75lb</t>
+        </is>
+      </c>
+      <c r="C29" s="4">
+        <v>60.0</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TT$ per 75lb bag</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retail bagged</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL (BAGGED)</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.facebook.com/marketplace/116087261735365/gravel/</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cycle 2 observation. Bagged retail, not comparable to bulk cubic-yard pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMCOL Hardware</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crusher run / blue metal</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT RETRIEVED</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8-yard load, per m3, and bagged</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Price not captured</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penal</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.amcolhardwarett.com/product-6222/8-yard-load-crusher-run--blue-metal.php</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cycle 2. Product lines confirmed across three pack sizes but no price was surfaced by search and the site cannot be fetched. Price NOT captured and NOT estimated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMCOL Hardware</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ballast (1/2 x 1/2 gravel with sharp sand)</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT RETRIEVED</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-yard and 11-yard loads</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Price not captured</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RETAIL</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not stated</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penal</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.amcolhardwarett.com/product-7960/1-load-12-x-12-gravel-w-sharp-sand-10-yards.php</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cycle 2. A blended product EcoEnergy could supply as components. Price NOT captured.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:K27"/>
+  <autoFilter ref="A5:K31"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -10795,7 +14867,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 2   |   12 September 2026  02:13 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 3   |   12 September 2026  04:32 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -10829,7 +14901,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">New prospects discovered this cycle</t>
+          <t xml:space="preserve">New prospects discovered, cycle 1</t>
         </is>
       </c>
       <c r="B6" s="3">
@@ -10837,350 +14909,354 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daily target is 25.</t>
+          <t xml:space="preserve">Directory and category sweep.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daily target</t>
+          <t xml:space="preserve">New prospects discovered, cycle 2</t>
         </is>
       </c>
       <c r="B7" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brief section 1.</t>
+          <t xml:space="preserve">Social, quarry-licensing and regional sweep requested with Metricool.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Performance against daily target</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192%</t>
-        </is>
+          <t xml:space="preserve">Total discovered today</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <v>74</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quality gate applied - no filler records.</t>
+          <t xml:space="preserve">Daily target is 25.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carried forward from prior canon</t>
+          <t xml:space="preserve">Daily target</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merged from the previous EcoEnergy workbook on 2026-09-12. Not counted against the daily target.</t>
+          <t xml:space="preserve">Brief section 1.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duplicates avoided on merge</t>
-        </is>
-      </c>
-      <c r="B10" s="3">
-        <v>1</v>
+          <t xml:space="preserve">Performance against daily target</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296%</t>
+        </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concrete Aggregate Suppliers was already held as ECO-0006 and was updated, not duplicated (section 10).</t>
+          <t xml:space="preserve">Quality gate applied - no filler records.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total prospects in pipeline</t>
+          <t xml:space="preserve">Carried forward from prior canon</t>
         </is>
       </c>
       <c r="B11" s="3">
-        <v>59</v>
-      </c>
-      <c r="C11" s="7"/>
+        <v>11</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merged from the previous EcoEnergy workbook on 2026-09-12. Not counted against the daily target.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BY PRIORITY</t>
-        </is>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duplicates avoided on merge</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Concrete Aggregate Suppliers was already held as ECO-0006 and was updated, not duplicated (section 10).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIER 1</t>
+          <t xml:space="preserve">Total prospects in pipeline</t>
         </is>
       </c>
       <c r="B13" s="3">
-        <v>31</v>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Highest-value recurring buyers and resellers.</t>
-        </is>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="C13" s="7"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TIER 2</t>
-        </is>
-      </c>
-      <c r="B14" s="3">
-        <v>19</v>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary commercial buyers.</t>
-        </is>
-      </c>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BY PRIORITY</t>
+        </is>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIER 3</t>
+          <t xml:space="preserve">TIER 1</t>
         </is>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low-volume but steady.</t>
+          <t xml:space="preserve">Highest-value recurring buyers and resellers.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BENCHMARK</t>
+          <t xml:space="preserve">TIER 2</t>
         </is>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Competitors and price references, not buyers.</t>
+          <t xml:space="preserve">Secondary commercial buyers.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BY SEGMENT</t>
-        </is>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 3</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low-volume but steady.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ready-mix and block producers</t>
+          <t xml:space="preserve">BENCHMARK</t>
         </is>
       </c>
       <c r="B18" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Highest continuous aggregate draw.</t>
+          <t xml:space="preserve">Competitors and price references, not buyers.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hardware stores and building-material resellers</t>
-        </is>
-      </c>
-      <c r="B19" s="3">
-        <v>20</v>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Already sell aggregate, therefore already buy it.</t>
-        </is>
-      </c>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BY SEGMENT</t>
+        </is>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contractors, civil, earthworks and drainage</t>
+          <t xml:space="preserve">Ready-mix and block producers</t>
         </is>
       </c>
       <c r="B20" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Project-driven volume.</t>
+          <t xml:space="preserve">Highest continuous aggregate draw.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">State developers and agencies</t>
+          <t xml:space="preserve">Hardware stores and building-material resellers</t>
         </is>
       </c>
       <c r="B21" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tender and vendor registration route.</t>
+          <t xml:space="preserve">Already sell aggregate, therefore already buy it.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trucking and haulage</t>
+          <t xml:space="preserve">Contractors, civil, earthworks and drainage</t>
         </is>
       </c>
       <c r="B22" s="3">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buyers and potential delivery partners.</t>
+          <t xml:space="preserve">Project-driven volume.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landscaping</t>
+          <t xml:space="preserve">State developers and agencies</t>
         </is>
       </c>
       <c r="B23" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Batch into one campaign.</t>
+          <t xml:space="preserve">Tender and vendor registration route.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COMMERCIAL ACTIVITY</t>
-        </is>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trucking and haulage</t>
+        </is>
+      </c>
+      <c r="B24" s="3">
+        <v>7</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buyers and potential delivery partners.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospects with a verified contact route</t>
+          <t xml:space="preserve">Landscaping</t>
         </is>
       </c>
       <c r="B25" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">All carried forward from prior canon. Telephone and e-mail for these were verified previously, not by this cycle's searches.</t>
+          <t xml:space="preserve">Batch into one campaign.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospects with NO contact route</t>
-        </is>
-      </c>
-      <c r="B26" s="3">
-        <v>47</v>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sourced and named, but no number or address could be verified from this environment. None invented.</t>
-        </is>
-      </c>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMERCIAL ACTIVITY</t>
+        </is>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outreach messages sent</t>
+          <t xml:space="preserve">Prospects with a verified contact route</t>
         </is>
       </c>
       <c r="B27" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cumosco and KAMCO, both by e-mail on 2026-09-12. Prior canon. This agent sent nothing.</t>
+          <t xml:space="preserve">All carried forward from prior canon. Telephone and e-mail for these were verified previously, not by this cycle's searches.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Responses received</t>
+          <t xml:space="preserve">Prospects with NO contact route</t>
         </is>
       </c>
       <c r="B28" s="3">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Both outbound e-mails are still pending a reply.</t>
+          <t xml:space="preserve">Sourced and named, but no number or address could be verified from this environment. None invented.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quote requests</t>
+          <t xml:space="preserve">Outreach messages sent</t>
         </is>
       </c>
       <c r="B29" s="3">
-        <v>0</v>
-      </c>
-      <c r="C29" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cumosco and KAMCO, both by e-mail on 2026-09-12. Prior canon. This agent sent nothing.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quotes issued</t>
+          <t xml:space="preserve">Responses received</t>
         </is>
       </c>
       <c r="B30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cumosco was quoted TT$125 / 195 / 205 per yd3 on 2026-09-12.</t>
+          <t xml:space="preserve">Both outbound e-mails are still pending a reply.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negotiations open</t>
+          <t xml:space="preserve">Quote requests</t>
         </is>
       </c>
       <c r="B31" s="3">
@@ -11191,44 +15267,44 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customers won</t>
+          <t xml:space="preserve">Quotes issued</t>
         </is>
       </c>
       <c r="B32" s="3">
+        <v>1</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cumosco was quoted TT$125 / 195 / 205 per yd3 on 2026-09-12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negotiations open</t>
+        </is>
+      </c>
+      <c r="B33" s="3">
         <v>0</v>
       </c>
-      <c r="C32" s="7"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRICING EXCEPTION - ACTION REQUIRED</t>
-        </is>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
+      <c r="C33" s="7"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cumosco quotation above list price</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CORRECTION DUE</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The 2026-09-12 quote of TT$125 / 195 / 205 per yd3 for pitrun / 3/8 / 3/4 sits ABOVE the canon list price of TT$77.63 / 167.06 / 167.06. Owner ruled on 2026-09-12 that the price list is canon, so a corrected quotation must be issued to Cumosco before any follow-up.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Customers won</t>
+        </is>
+      </c>
+      <c r="B34" s="3">
+        <v>0</v>
+      </c>
+      <c r="C34" s="7"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRICING</t>
+          <t xml:space="preserve">PRICING EXCEPTION - ACTION REQUIRED</t>
         </is>
       </c>
       <c r="B35" s="6"/>
@@ -11237,160 +15313,408 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Materials with an EcoEnergy base price</t>
+          <t xml:space="preserve">Cumosco quotation above list price</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 of 7</t>
+          <t xml:space="preserve">CORRECTION DUE</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4 gravel, 3/8 gravel, sharp sand, plastering sand.</t>
+          <t xml:space="preserve">The 2026-09-12 quote of TT$125 / 195 / 205 per yd3 for pitrun / 3/8 / 3/4 sits ABOVE the canon list price of TT$77.63 / 167.06 / 167.06. Owner ruled on 2026-09-12 that the price list is canon, so a corrected quotation must be issued to Cumosco before any follow-up.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Materials flagged MARKET VERIFICATION REQUIRED</t>
-        </is>
-      </c>
-      <c r="B37" s="3">
-        <v>0</v>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pitrun and sandfill/backfill - no published T&amp;T price found.</t>
-        </is>
-      </c>
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRICING</t>
+        </is>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pricing rule applied</t>
+          <t xml:space="preserve">Materials with an EcoEnergy base price</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Benchmark x 0.90</t>
+          <t xml:space="preserve">7 of 7</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">10% below verified market benchmark.</t>
+          <t xml:space="preserve">3/4 gravel, 3/8 gravel, sharp sand, plastering sand.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maximum negotiated discount</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30%</t>
-        </is>
+          <t xml:space="preserve">Materials flagged MARKET VERIFICATION REQUIRED</t>
+        </is>
+      </c>
+      <c r="B39" s="3">
+        <v>0</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Closing tool. Never automatic, never advertised.</t>
+          <t xml:space="preserve">Pitrun and sandfill/backfill - no published T&amp;T price found.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Next scheduled market review</t>
+          <t xml:space="preserve">Pricing rule applied</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-13 23:59 (Sunday, Trinidad time, AST/UTC-4)</t>
+          <t xml:space="preserve">Benchmark x 0.90</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brief section 6.</t>
+          <t xml:space="preserve">10% below verified market benchmark.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BLOCKERS - REQUIRE HUMAN ACTION</t>
-        </is>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maximum negotiated discount</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30%</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Closing tool. Never automatic, never advertised.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Contact details for the discovered prospects</t>
+          <t xml:space="preserve">Next scheduled market review</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLOCKING</t>
+          <t xml:space="preserve">2026-09-13 23:59 (Sunday, Trinidad time, AST/UTC-4)</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">47 of 59 prospects have no verified contact route. Directory and company pages (findyello.com, nqcl.co.tt, energy.gov.tt, tt.directory) are refused by the egress proxy. Allowlist those hosts, or supply the details from a machine with ordinary web access.</t>
+          <t xml:space="preserve">Brief section 6.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. Messaging integration</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BLOCKING</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No authorised e-mail or messaging tool is connected to this agent. The two e-mails on record were sent outside it, through Outlook. Until an integration is authorised, outreach cannot be executed here even for the 12 prospects that do have a contact route.</t>
-        </is>
-      </c>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHANNEL ACCESS - VERIFIED THIS CYCLE</t>
+        </is>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. NQCL price list PDF</t>
+          <t xml:space="preserve">Metricool MCP connector</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTIALLY RESOLVED</t>
+          <t xml:space="preserve">CONNECTED</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The pitrun benchmark of TT$86.25/yd3 was recovered from prior canon, so pitrun is now priced. The PDF itself is still blocked, and it is effective 31-Aug-2022, so the benchmark is four years old.</t>
+          <t xml:space="preserve">Authenticated and responding. It returned 4 brands, all personal or Iseldoran Sagas accounts: kerron.pierre5, thekerron, kerron347, kerron.shaul.pier and IseldoranSagas.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">EcoEnergy brand in Metricool</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT PRESENT</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No EcoEnergy brand exists in the account, so Metricool cannot publish for EcoEnergy or report EcoEnergy analytics. Nothing was posted to the personal accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metricool as a prospecting tool</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT CAPABLE</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Its toolset is scheduling, analytics and best-time-to-post for accounts you own. It cannot search Facebook, Instagram, TikTok, X or Threads for third-party prospects or prices. Its only third-party feature is competitor tracking on Instagram, Facebook, Twitch, YouTube, X and Bluesky, and that needs an EcoEnergy brand first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facebook / Instagram / TikTok / X / Threads</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLATFORM NOT ACCESSIBLE</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Direct connection to facebook.com, instagram.com, tiktok.com, x.com and threads.net was tested this cycle and every one was refused by the network egress policy. Social findings below came from public search indexing of those pages, not from browsing them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARKET INTELLIGENCE - CYCLE 2</t>
+        </is>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 quarries voluntarily shut in a licensing dispute</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VERIFIED</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In November 2025 the newly formed Trinidad and Tobago Aggregate Producers Alliance (TTAPA) closed 24 member quarries nationwide over the Government's failure to issue overdue processing licences. TTAPA's president warned that as many as 100,000 construction jobs were at risk.  IMPLICATION: A supply shock in the aggregate market. Buyers who lost their supplier are actively looking for one. This is the strongest commercial opening available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate shortfall feared as demand outruns production</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VERIFIED</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reporting describes a widening gap between aggregate demand and production capacity as major infrastructure projects move forward.  IMPLICATION: Demand-led market. Supply reliability outranks price for many buyers, which supports holding the base price rather than discounting early.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licensing structure: 9 full licences, the rest on hold-over permits</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VERIFIED</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nine companies hold full licences to mine or process aggregate. Another 13 operate under temporary hold-over permits granted by the line minister. The Ministry states 25 bona fide operators received hold-over letters on 22 May.  IMPLICATION: Licence status is now a commercial differentiator. A buyer facing a police crackdown on illegal material wants a supplier whose paperwork is sound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Police crackdown on illegal quarries</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VERIFIED</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newsday reported in November 2025 that police moved against illegal quarrying operations.  IMPLICATION: Buyers sourcing from unlicensed operators carry real risk. Licensed supply is worth a premium to any contractor on a government project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named licensed quarry operations</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VERIFIED</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reported licensed operations include Bestcrete (Melajo Forest Reserve, Matura), ANSA McAL (Depot Road, Longdenville), Mineral Mines of Trinidad (Vega de Oropouche), EMBD (Coco Road, Claxton Bay and Milton Village, Couva), AADS Multi-Tasking (Rio Grande Trace, Matura), Firma Fabrication and Construction (Melajo Forest Reserve, Sangre Grande) and Seereeram Brothers (Cangrejal Road, Santa Cruz).  IMPLICATION: This is the competitor map. Seereeram Brothers was previously held as a contractor prospect and has been reclassified as a producer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN QUESTION: EcoEnergy's own licence status is not established</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The shortage and crackdown make licensed supply a strong selling position, but EcoEnergy's own licence or hold-over permit status is not recorded anywhere in this pipeline and was not supplied.  IMPLICATION: BLOCKING for the licence-led pitch. Confirm EcoEnergy's status before any outreach claims licensed supply. Do not make the claim until it is confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKERS - REQUIRE HUMAN ACTION</t>
+        </is>
+      </c>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Contact details for the discovered prospects</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKING</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71 of 85 prospects have no verified contact route. Directory and company pages (findyello.com, nqcl.co.tt, energy.gov.tt, tt.directory) are refused by the egress proxy. Allowlist those hosts, or supply the details from a machine with ordinary web access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Messaging integration</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKING</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No authorised e-mail or messaging tool is connected to this agent. The two e-mails on record were sent outside it, through Outlook. Until an integration is authorised, outreach cannot be executed here even for the 14 prospects that do have a contact route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. NQCL price list PDF</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIALLY RESOLVED</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The pitrun benchmark of TT$86.25/yd3 was recovered from prior canon, so pitrun is now priced. The PDF itself is still blocked, and it is effective 31-Aug-2022, so the benchmark is four years old.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">4. Social comment mining</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">NOT ACCESSIBLE</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Facebook, Instagram, X and Threads are not reachable from this environment. Section 4 comment mining could not be run beyond what public search indexes surfaced.</t>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facebook, Instagram, X and Threads are not reachable from this environment. Section 4 comment mining could not be run beyond what public search indexes surfaced. Three active T&amp;T buyer groups were located and are named in the weekly report for someone with Facebook access to mine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. EcoEnergy quarry licence status</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKING THE STRONGEST PITCH</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 quarries shut in a licensing dispute and police are acting against illegal operations, which makes licensed supply a powerful selling position. EcoEnergy's own licence or hold-over permit status is not recorded anywhere and was not supplied. Do NOT claim licensed supply in outreach until confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Metricool EcoEnergy brand</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACTION</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Create an EcoEnergy brand in Metricool and connect its Facebook and Instagram pages. That enables competitor tracking on rival aggregate sellers and gives EcoEnergy an inbound lead channel.</t>
         </is>
       </c>
     </row>
@@ -11400,7 +15724,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11422,7 +15746,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 2   |   12 September 2026  02:13 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 3   |   12 September 2026  04:32 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -12599,12 +16923,12 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIER 1</t>
+          <t xml:space="preserve">BENCHMARK</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Earthworks / civil contractor</t>
+          <t xml:space="preserve">Earthworks contractor + LICENSED QUARRY OPERATOR</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -13654,50 +17978,1012 @@
         </is>
       </c>
     </row>
-    <row r="65"/>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0060</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Class Gravel &amp; Aggregates</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aggregate reseller</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A dedicated gravel and aggregate business, so it must buy from a quarry.</t>
+        </is>
+      </c>
+    </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0061</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roopnarine Hardware Limited</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Discovered this cycle</t>
         </is>
       </c>
-      <c r="B66" s="3">
-        <v>48</v>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACTIVE ADVERTISEMENT: 'Gravel, Sharp Sand, Red Sand. Delivery available.' Currently trading aggregate.</t>
+        </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0062</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B Chadee &amp; Sons Stockpile and Hardware Supplies Ltd</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stockpile operator / hardware</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operates a STOCKPILE segregating material grades and maintaining steady supply, with a rental and aggregate division.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0063</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Northeastern Hardware Ltd</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / reseller</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware business in Sangre Grande, close to the Guaico and Matura quarry belt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0064</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C.J. Lumber Ltd</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumber / building materials</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Established building materials supplier in the central construction corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0065</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samlal Seepersad Hardware Limited</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / building supplies</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplying building materials nationally for over 50 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0066</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Island Roofing &amp; Hardware Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / roofing</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies lumber, roofing materials and general hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0067</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aqucan Hardware and Construction Ltd</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware + construction</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies construction tools and accessories and carries out construction work, so it both buys and uses material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0068</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discount Hardware And Building Supplies</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware / building supplies</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discount building supplies business, so it competes on price and is sensitive to purchase cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0069</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sands Parry</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand and gravel supplier</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed under sand and gravel in a national directory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0070</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinity Readymix Limited</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ready-mix concrete producer</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two batching plants, at Penal and Point Lisas, so sand and gravel draw is continuous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0071</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Central Concrete Product Ltd</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Precast concrete manufacturer</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Market leader in precast concrete products, incorporated 1976. Precast production consumes graded aggregate continuously.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0072</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRESTCON 2021 Limited</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Precast / prestressed concrete</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manufactures precast and prestressed products for bridges, docks, jetties, marinas and petrochemical structures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0073</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">General Earth Movers Limited (GEML)</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphalt / civil contractor</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Produces hot mix asphalt from a wide range of aggregate combinations, and performs milling and paving at scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0074</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Danny's Enterprises Company Limited (DECL)</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roadworks / drainage contractor</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roadworks, asphalt paving and installation of wick and earthquake drains, all aggregate-intensive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0075</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lake Asphalt of Trinidad and Tobago (1978) Limited</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State asphalt producer</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State asphalt producer. Asphalt manufacture requires aggregate blending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0076</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphalt Paving Co Ltd</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphalt paving contractor</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Directory-listed asphalt paving contractor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0077</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad Asphalt Pavers General Contractors Ltd</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphalt / general contractor</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Directory-listed asphalt and general contracting firm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0078</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weathershield Systems Caribbean Limited</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 3</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asphalt / waterproofing contractor</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Founded 1994, successor to Trinidad Mastic Asphalt &amp; Contracting Company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0079</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mineral Mines of Trinidad Limited</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENCHMARK</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licensed quarry operator</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holds a licence to mine or process aggregate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0080</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estate Management and Business Development Company Limited (EMBD)</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENCHMARK</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State land company / licensed quarry</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holds licensed quarry operations at two sites.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0081</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AADS Multi-Tasking Limited</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENCHMARK</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licensed quarry operator</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holds a licence to mine or process aggregate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0082</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Firma Fabrication and Construction Limited</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 3</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licensed quarry operator + contractor</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holds a licensed quarry and also carries out fabrication and construction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0083</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conveyor and Plant Solutions</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 3</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant and conveyor supplier</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies conveyor and plant equipment to the quarry and materials sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0084</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Christle Limited</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 3</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial supplier</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed in the manufacturers association wholesale directory with a published telephone number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0085</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad and Tobago Aggregate Producers Alliance (TTAPA)</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENCHMARK</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industry association</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newly formed alliance representing aggregate producers. Led the November 2025 shutdown of 24 quarries over processing licences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91"/>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="B92" s="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Merged from prior canon</t>
         </is>
       </c>
-      <c r="B67" s="3">
+      <c r="B93" s="3">
         <v>11</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Weekly target</t>
         </is>
       </c>
-      <c r="B68" s="3">
+      <c r="B94" s="3">
         <v>175</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Against weekly target (discovered only)</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27%</t>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G69"/>
+  <autoFilter ref="A5:G95"/>
 </worksheet>
 </file>
--- a/ecoenergy/EcoEnergy_Aggregate_Sales_Pipeline.xlsx
+++ b/ecoenergy/EcoEnergy_Aggregate_Sales_Pipeline.xlsx
@@ -175,7 +175,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 3   |   12 September 2026  04:32 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 4   |   12 September 2026  04:44 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -12542,7 +12542,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -12572,14 +12572,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 3   |   12 September 2026  04:32 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 4   |   12 September 2026  04:44 (Trinidad time)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A message is recorded here ONLY when a send was confirmed. The two entries below are prior canon carried forward from the previous EcoEnergy workbook.</t>
+          <t xml:space="preserve">A message is recorded here ONLY when a tool confirmed the action. Two e-mail entries are prior canon carried forward from the previous EcoEnergy workbook. The social entry is SCHEDULED and confirmed by Metricool, not yet published.</t>
         </is>
       </c>
     </row>
@@ -12804,6 +12804,79 @@
       <c r="O7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Prior canon - Outlook send action</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12 (scheduled for 2026-09-14 11:00 AST)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BROADCAST</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public audience, kerron.pierre5 brand (Facebook, LinkedIn, Threads)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social, via Metricool</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outbound</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kerron.pierre5 brand followers</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wholesale aggregate supply offer, scheduled post</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; plastering sand; backfill; sandfill</t>
+        </is>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No figure published. Positioning only: about 10% under market.</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes. Up to 30%, stated as subject to quantity and terms.</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT YET PUBLISHED. Scheduled, awaiting the publication time.</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After publication at 2026-09-14 11:00 AST, check delivery on all three networks and route any inbound enquiry into the pipeline as a new prospect.</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metricool MCP. Post id 374817136, uuid 5571315352575427490. Tool confirmed status PENDING on facebook, linkedin and threads with autoPublish true. SCHEDULED, NOT SENT.</t>
         </is>
       </c>
     </row>
@@ -12839,7 +12912,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 3   |   12 September 2026  04:32 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 4   |   12 September 2026  04:44 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -13327,7 +13400,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 3   |   12 September 2026  04:32 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 4   |   12 September 2026  04:44 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14922,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -14867,7 +14940,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 3   |   12 September 2026  04:32 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 4   |   12 September 2026  04:44 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -15453,113 +15526,113 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT PRESENT</t>
+          <t xml:space="preserve">STILL NOT PRESENT</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">No EcoEnergy brand exists in the account, so Metricool cannot publish for EcoEnergy or report EcoEnergy analytics. Nothing was posted to the personal accounts.</t>
+          <t xml:space="preserve">No EcoEnergy brand exists. On owner instruction the kerron.pierre5 brand was used instead to publish the EcoEnergy offer.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricool as a prospecting tool</t>
+          <t xml:space="preserve">Scheduled post via kerron.pierre5</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT CAPABLE</t>
+          <t xml:space="preserve">CONFIRMED</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Its toolset is scheduling, analytics and best-time-to-post for accounts you own. It cannot search Facebook, Instagram, TikTok, X or Threads for third-party prospects or prices. Its only third-party feature is competitor tracking on Instagram, Facebook, Twitch, YouTube, X and Bluesky, and that needs an EcoEnergy brand first.</t>
+          <t xml:space="preserve">Post id 374817136 scheduled for 2026-09-14 11:00 Trinidad time (17:00 Europe/Madrid) to Facebook, LinkedIn and Threads, autoPublish on. Tool returned status PENDING on all three. SCHEDULED, NOT YET PUBLISHED.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facebook / Instagram / TikTok / X / Threads</t>
+          <t xml:space="preserve">Networks excluded from that post</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLATFORM NOT ACCESSIBLE</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direct connection to facebook.com, instagram.com, tiktok.com, x.com and threads.net was tested this cycle and every one was refused by the network egress policy. Social findings below came from public search indexing of those pages, not from browsing them.</t>
+          <t xml:space="preserve">Instagram, TikTok and YouTube require an image or video and none was available. X was excluded because that handle is IseldoranSagas, a separate novel brand.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MARKET INTELLIGENCE - CYCLE 2</t>
-        </is>
-      </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metricool competitor tracking</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EMPTY</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Queried for the brand over the last 30 days and returned no rows, because no competitors are configured. This is Metricool's only third-party data surface.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 quarries voluntarily shut in a licensing dispute</t>
+          <t xml:space="preserve">Metricool as a prospecting tool</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">NOT CAPABLE</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">In November 2025 the newly formed Trinidad and Tobago Aggregate Producers Alliance (TTAPA) closed 24 member quarries nationwide over the Government's failure to issue overdue processing licences. TTAPA's president warned that as many as 100,000 construction jobs were at risk.  IMPLICATION: A supply shock in the aggregate market. Buyers who lost their supplier are actively looking for one. This is the strongest commercial opening available.</t>
+          <t xml:space="preserve">Its toolset is scheduling, analytics and best-time-to-post for accounts you own. It cannot search Facebook, Instagram, TikTok, X or Threads for third-party prospects or prices. Its only third-party feature is competitor tracking on Instagram, Facebook, Twitch, YouTube, X and Bluesky, and that needs an EcoEnergy brand first.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aggregate shortfall feared as demand outruns production</t>
+          <t xml:space="preserve">Facebook / Instagram / TikTok / X / Threads</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">PLATFORM NOT ACCESSIBLE</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporting describes a widening gap between aggregate demand and production capacity as major infrastructure projects move forward.  IMPLICATION: Demand-led market. Supply reliability outranks price for many buyers, which supports holding the base price rather than discounting early.</t>
+          <t xml:space="preserve">Direct connection to facebook.com, instagram.com, tiktok.com, x.com and threads.net was tested this cycle and every one was refused by the network egress policy. Social findings below came from public search indexing of those pages, not from browsing them.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Licensing structure: 9 full licences, the rest on hold-over permits</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VERIFIED</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nine companies hold full licences to mine or process aggregate. Another 13 operate under temporary hold-over permits granted by the line minister. The Ministry states 25 bona fide operators received hold-over letters on 22 May.  IMPLICATION: Licence status is now a commercial differentiator. A buyer facing a police crackdown on illegal material wants a supplier whose paperwork is sound.</t>
-        </is>
-      </c>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARKET INTELLIGENCE - CYCLE 2</t>
+        </is>
+      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Police crackdown on illegal quarries</t>
+          <t xml:space="preserve">24 quarries voluntarily shut in a licensing dispute</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -15569,14 +15642,14 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newsday reported in November 2025 that police moved against illegal quarrying operations.  IMPLICATION: Buyers sourcing from unlicensed operators carry real risk. Licensed supply is worth a premium to any contractor on a government project.</t>
+          <t xml:space="preserve">In November 2025 the newly formed Trinidad and Tobago Aggregate Producers Alliance (TTAPA) closed 24 member quarries nationwide over the Government's failure to issue overdue processing licences. TTAPA's president warned that as many as 100,000 construction jobs were at risk.  IMPLICATION: A supply shock in the aggregate market. Buyers who lost their supplier are actively looking for one. This is the strongest commercial opening available.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Named licensed quarry operations</t>
+          <t xml:space="preserve">Aggregate shortfall feared as demand outruns production</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -15586,133 +15659,218 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reported licensed operations include Bestcrete (Melajo Forest Reserve, Matura), ANSA McAL (Depot Road, Longdenville), Mineral Mines of Trinidad (Vega de Oropouche), EMBD (Coco Road, Claxton Bay and Milton Village, Couva), AADS Multi-Tasking (Rio Grande Trace, Matura), Firma Fabrication and Construction (Melajo Forest Reserve, Sangre Grande) and Seereeram Brothers (Cangrejal Road, Santa Cruz).  IMPLICATION: This is the competitor map. Seereeram Brothers was previously held as a contractor prospect and has been reclassified as a producer.</t>
+          <t xml:space="preserve">Reporting describes a widening gap between aggregate demand and production capacity as major infrastructure projects move forward.  IMPLICATION: Demand-led market. Supply reliability outranks price for many buyers, which supports holding the base price rather than discounting early.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN QUESTION: EcoEnergy's own licence status is not established</t>
+          <t xml:space="preserve">Licensing structure: 9 full licences, the rest on hold-over permits</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The shortage and crackdown make licensed supply a strong selling position, but EcoEnergy's own licence or hold-over permit status is not recorded anywhere in this pipeline and was not supplied.  IMPLICATION: BLOCKING for the licence-led pitch. Confirm EcoEnergy's status before any outreach claims licensed supply. Do not make the claim until it is confirmed.</t>
+          <t xml:space="preserve">Nine companies hold full licences to mine or process aggregate. Another 13 operate under temporary hold-over permits granted by the line minister. The Ministry states 25 bona fide operators received hold-over letters on 22 May.  IMPLICATION: Licence status is now a commercial differentiator. A buyer facing a police crackdown on illegal material wants a supplier whose paperwork is sound.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BLOCKERS - REQUIRE HUMAN ACTION</t>
-        </is>
-      </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Police crackdown on illegal quarries</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VERIFIED</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newsday reported in November 2025 that police moved against illegal quarrying operations.  IMPLICATION: Buyers sourcing from unlicensed operators carry real risk. Licensed supply is worth a premium to any contractor on a government project.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Contact details for the discovered prospects</t>
+          <t xml:space="preserve">Named licensed quarry operations</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLOCKING</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">71 of 85 prospects have no verified contact route. Directory and company pages (findyello.com, nqcl.co.tt, energy.gov.tt, tt.directory) are refused by the egress proxy. Allowlist those hosts, or supply the details from a machine with ordinary web access.</t>
+          <t xml:space="preserve">Reported licensed operations include Bestcrete (Melajo Forest Reserve, Matura), ANSA McAL (Depot Road, Longdenville), Mineral Mines of Trinidad (Vega de Oropouche), EMBD (Coco Road, Claxton Bay and Milton Village, Couva), AADS Multi-Tasking (Rio Grande Trace, Matura), Firma Fabrication and Construction (Melajo Forest Reserve, Sangre Grande) and Seereeram Brothers (Cangrejal Road, Santa Cruz).  IMPLICATION: This is the competitor map. Seereeram Brothers was previously held as a contractor prospect and has been reclassified as a producer.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Messaging integration</t>
+          <t xml:space="preserve">OPEN QUESTION: EcoEnergy's own licence status is not established</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLOCKING</t>
+          <t xml:space="preserve">NOT VERIFIED</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">No authorised e-mail or messaging tool is connected to this agent. The two e-mails on record were sent outside it, through Outlook. Until an integration is authorised, outreach cannot be executed here even for the 14 prospects that do have a contact route.</t>
+          <t xml:space="preserve">The shortage and crackdown make licensed supply a strong selling position, but EcoEnergy's own licence or hold-over permit status is not recorded anywhere in this pipeline and was not supplied.  IMPLICATION: BLOCKING for the licence-led pitch. Confirm EcoEnergy's status before any outreach claims licensed supply. Do not make the claim until it is confirmed.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. NQCL price list PDF</t>
+          <t xml:space="preserve">Metricool competitor tracking returned no data</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTIALLY RESOLVED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The pitrun benchmark of TT$86.25/yd3 was recovered from prior canon, so pitrun is now priced. The PDF itself is still blocked, and it is effective 31-Aug-2022, so the benchmark is four years old.</t>
+          <t xml:space="preserve">The competitors connector was queried for the kerron.pierre5 brand over 2026-08-13 to 2026-09-12 for Facebook competitor screen name, display name, followers and posts. It returned an empty result set, because no competitors are configured on the brand.  IMPLICATION: Metricool's only third-party data surface is competitor tracking, and it is empty. Adding rival aggregate sellers as competitors would turn it into a genuine monitoring channel. It still cannot search for prospects or prices.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. Social comment mining</t>
+          <t xml:space="preserve">Best-time-to-post data reflects the wrong audience</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT ACCESSIBLE</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facebook, Instagram, X and Threads are not reachable from this environment. Section 4 comment mining could not be run beyond what public search indexes surfaced. Three active T&amp;T buyer groups were located and are named in the weekly report for someone with Facebook access to mine.</t>
+          <t xml:space="preserve">Metricool returned Facebook best-time data for the kerron.pierre5 brand. The strongest hours sit around 10:00 to 12:00 Europe/Madrid, which is 04:00 to 06:00 in Trinidad. The brand's timezone is set to Europe/Madrid and its audience is the existing personal and Iseldoran Sagas following, not Trinidad construction buyers.  IMPLICATION: The engagement peaks are not a guide for a Trinidad B2B audience. The post was instead scheduled at 17:00 Madrid, which is 11:00 Trinidad, the strongest hour in the data that still falls inside Trinidad business hours. Set the brand timezone to America/Port_of_Spain if EcoEnergy will keep using it.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5. EcoEnergy quarry licence status</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BLOCKING THE STRONGEST PITCH</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24 quarries shut in a licensing dispute and police are acting against illegal operations, which makes licensed supply a powerful selling position. EcoEnergy's own licence or hold-over permit status is not recorded anywhere and was not supplied. Do NOT claim licensed supply in outreach until confirmed.</t>
-        </is>
-      </c>
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKERS - REQUIRE HUMAN ACTION</t>
+        </is>
+      </c>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">1. Contact details for the discovered prospects</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKING</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71 of 85 prospects have no verified contact route. Directory and company pages (findyello.com, nqcl.co.tt, energy.gov.tt, tt.directory) are refused by the egress proxy. Allowlist those hosts, or supply the details from a machine with ordinary web access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Messaging integration</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKING</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No authorised e-mail or messaging tool is connected to this agent. The two e-mails on record were sent outside it, through Outlook. Until an integration is authorised, outreach cannot be executed here even for the 14 prospects that do have a contact route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. NQCL price list PDF</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIALLY RESOLVED</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The pitrun benchmark of TT$86.25/yd3 was recovered from prior canon, so pitrun is now priced. The PDF itself is still blocked, and it is effective 31-Aug-2022, so the benchmark is four years old.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Social comment mining</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT ACCESSIBLE</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facebook, Instagram, X and Threads are not reachable from this environment. Section 4 comment mining could not be run beyond what public search indexes surfaced. Three active T&amp;T buyer groups were located and are named in the weekly report for someone with Facebook access to mine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. EcoEnergy quarry licence status</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKING THE STRONGEST PITCH</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 quarries shut in a licensing dispute and police are acting against illegal operations, which makes licensed supply a powerful selling position. EcoEnergy's own licence or hold-over permit status is not recorded anywhere and was not supplied. Do NOT claim licensed supply in outreach until confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">6. Metricool EcoEnergy brand</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ACTION</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Create an EcoEnergy brand in Metricool and connect its Facebook and Instagram pages. That enables competitor tracking on rival aggregate sellers and gives EcoEnergy an inbound lead channel.</t>
         </is>
@@ -15746,7 +15904,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 3   |   12 September 2026  04:32 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 4   |   12 September 2026  04:44 (Trinidad time)</t>
         </is>
       </c>
     </row>

--- a/ecoenergy/EcoEnergy_Aggregate_Sales_Pipeline.xlsx
+++ b/ecoenergy/EcoEnergy_Aggregate_Sales_Pipeline.xlsx
@@ -130,7 +130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AE117"/>
+  <dimension ref="A1:AE145"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -176,7 +176,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 5   |   12 September 2026  04:51 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 6   |   12 September 2026  05:47 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PENDING VERIFICATION</t>
+          <t xml:space="preserve">https://www.facebook.com/trinidadcontractorsltd/</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AE32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Established 1959. Sea defence and precast work implies armour stone and high-spec aggregate demand. Contractor profile - aggregate is a project input. Volume is lumpy and project-driven, so qualify on current project pipeline, not on history.</t>
+          <t xml:space="preserve">Established 1959. Sea defence and precast work implies armour stone and high-spec aggregate demand. Contractor profile - aggregate is a project input. Volume is lumpy and project-driven, so qualify on current project pipeline, not on history. | CYCLE 5 UPDATE (2026-09-12): Facebook business page identified at facebook.com/trinidadcontractorsltd, San Fernando.</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIER 2</t>
+          <t xml:space="preserve">TIER 1</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -5834,12 +5834,12 @@
       </c>
       <c r="AD43" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identify procurement portal and vendor registration requirements.</t>
+          <t xml:space="preserve">Register as an approved supplier with NIPDEC. This is the single highest-leverage registration available: it gates PURE road rehabilitation procurement.</t>
         </is>
       </c>
       <c r="AE43" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revenue figure is third-party and unverified. NIPDEC also acts as a procurement agent for other state bodies, which multiplies reach. STATE ENTITY - purchasing runs through formal tender and vendor registration. The action is to register as an approved supplier, not to cold-sell. Long lead time, very high volume.</t>
+          <t xml:space="preserve">Revenue figure is third-party and unverified. NIPDEC also acts as a procurement agent for other state bodies, which multiplies reach. STATE ENTITY - purchasing runs through formal tender and vendor registration. The action is to register as an approved supplier, not to cold-sell. Long lead time, very high volume. | CYCLE 5 UPDATE (2026-09-12): MATERIALLY MORE IMPORTANT THAN FIRST RECORDED. NIPDEC has been the authorised procurement agency for the Ministry of Works PURE road programme since 2002. It is therefore the procurement gateway for national road rehabilitation, not merely a property developer. Supplier registration here reaches the largest aggregate-consuming programme in the country.</t>
         </is>
       </c>
     </row>
@@ -17097,8 +17097,4292 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0113</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couva/Tabaquite/Talparo Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Railway Road, Couva</t>
+        </is>
+      </c>
+      <c r="I118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.facebook.com/CouvaTabaquiteTalparoRegionalCorporation/</t>
+        </is>
+      </c>
+      <c r="M118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://cttrc.gov.tt/</t>
+        </is>
+      </c>
+      <c r="Q118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://cttrc.gov.tt/procurement/</t>
+        </is>
+      </c>
+      <c r="S118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROCUREMENT PAGE CONFIRMED, listing categories 'Drainage and Irrigation' and 'Local Roads and Bridges'. The clearest documented public-sector aggregate requirement found so far. Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB118" s="7"/>
+      <c r="AC118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. TOP PRIORITY of the 14. Its procurement page names the exact categories EcoEnergy supplies, and Couva is the number one area in the section 18 geographic priority list. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0114</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sangre Grande Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sangre Grande</t>
+        </is>
+      </c>
+      <c r="I119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rdlg.gov.tt/municipal-corporations/</t>
+        </is>
+      </c>
+      <c r="S119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB119" s="7"/>
+      <c r="AC119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Sits beside the NQCL Guaico sand and gravel division and the Matura quarry belt, so haulage is short. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0115</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penal/Debe Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penal / Debe</t>
+        </is>
+      </c>
+      <c r="I120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rdlg.gov.tt/municipal-corporations/</t>
+        </is>
+      </c>
+      <c r="S120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB120" s="7"/>
+      <c r="AC120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Penal and Debe are both section 18 priority areas. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0116</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Princes Town Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Princes Town</t>
+        </is>
+      </c>
+      <c r="I121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rdlg.gov.tt/municipal-corporations/</t>
+        </is>
+      </c>
+      <c r="S121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB121" s="7"/>
+      <c r="AC121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Princes Town is a section 18 priority area. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0117</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chaguanas Borough Corporation</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chaguanas</t>
+        </is>
+      </c>
+      <c r="I122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rdlg.gov.tt/municipal-corporations/</t>
+        </is>
+      </c>
+      <c r="S122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB122" s="7"/>
+      <c r="AC122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Chaguanas is a section 18 priority area and the fastest-growing borough. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0118</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arima Borough Corporation</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arima</t>
+        </is>
+      </c>
+      <c r="I123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rdlg.gov.tt/municipal-corporations/</t>
+        </is>
+      </c>
+      <c r="S123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB123" s="7"/>
+      <c r="AC123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Arima is a section 18 priority area. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0119</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Fernando City Corporation</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Fernando</t>
+        </is>
+      </c>
+      <c r="I124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rdlg.gov.tt/municipal-corporations/</t>
+        </is>
+      </c>
+      <c r="S124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB124" s="7"/>
+      <c r="AC124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. San Fernando is a section 18 priority area and the southern commercial centre. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0120</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Port of Spain City Corporation</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Port of Spain</t>
+        </is>
+      </c>
+      <c r="I125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rdlg.gov.tt/municipal-corporations/</t>
+        </is>
+      </c>
+      <c r="S125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB125" s="7"/>
+      <c r="AC125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Capital city corporation. Dense urban drainage and road maintenance load. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0121</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diego Martin Borough Corporation</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diego Martin</t>
+        </is>
+      </c>
+      <c r="I126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dmbc.gov.tt/</t>
+        </is>
+      </c>
+      <c r="Q126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dmbc.gov.tt/lga/</t>
+        </is>
+      </c>
+      <c r="S126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB126" s="7"/>
+      <c r="AC126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Declared a borough in 2023. Hillside terrain means heavy slope and drainage works. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0122</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Siparia Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Siparia</t>
+        </is>
+      </c>
+      <c r="I127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rdlg.gov.tt/municipal-corporations/</t>
+        </is>
+      </c>
+      <c r="S127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB127" s="7"/>
+      <c r="AC127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Declared a borough in 2023 alongside Diego Martin. Covers the deep south. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0123</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Juan/Laventille Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Juan / Laventille</t>
+        </is>
+      </c>
+      <c r="I128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rdlg.gov.tt/municipal-corporations/</t>
+        </is>
+      </c>
+      <c r="S128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB128" s="7"/>
+      <c r="AC128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Dense urban corridor with continuous road and drainage maintenance. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0124</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tunapuna/Piarco Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tunapuna / Piarco</t>
+        </is>
+      </c>
+      <c r="I129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rdlg.gov.tt/municipal-corporations/</t>
+        </is>
+      </c>
+      <c r="S129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB129" s="7"/>
+      <c r="AC129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Large east-west corridor region covering Arouca, Trincity, D'Abadie and Maloney. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0125</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mayaro/Rio Claro Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mayaro / Rio Claro</t>
+        </is>
+      </c>
+      <c r="I130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://mayarorioclaro.com/</t>
+        </is>
+      </c>
+      <c r="Q130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://mayarorioclaro.com/timeline_slider_post/municipal-corporation/</t>
+        </is>
+      </c>
+      <c r="S130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB130" s="7"/>
+      <c r="AC130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Rural east with long access roads and a heavy agricultural access road burden. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0126</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Point Fortin Borough Corporation</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Point Fortin</t>
+        </is>
+      </c>
+      <c r="I131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Rural Development and Local Government (via public search index)</t>
+        </is>
+      </c>
+      <c r="R131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rdlg.gov.tt/municipal-corporations/</t>
+        </is>
+      </c>
+      <c r="S131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+      <c r="T131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB131" s="7"/>
+      <c r="AC131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Locate the corporation's procurement or tenders page and register EcoEnergy as an approved aggregate supplier. Then track notices for local roads and drainage works.</t>
+        </is>
+      </c>
+      <c r="AE131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Southwestern borough serving the energy corridor. One of the 14 municipal corporations. Local roads and drainage are core statutory functions with annual budget allocations, so aggregate demand is recurring and plannable rather than one-off. Purchasing runs through formal procurement, so the action is supplier registration, not a cold sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0127</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Works and Transport - PURE Unit</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">National road rehabilitation programme</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad (nationwide)</t>
+        </is>
+      </c>
+      <c r="I132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mowt.gov.tt/</t>
+        </is>
+      </c>
+      <c r="Q132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Web Search (public index)</t>
+        </is>
+      </c>
+      <c r="R132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://mowt.gov.tt/Divisions/Programme-For-Upgrading-Roads-Efficiency-(PURE)-Un/Procurement</t>
+        </is>
+      </c>
+      <c r="S132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme for Upgrading Roads Efficiency. Tenders cover slope stabilisation, road work, bridge reconstruction and alternative access routes, all heavy aggregate consumers. Has a live procurement page inviting contractors to tender.</t>
+        </is>
+      </c>
+      <c r="T132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB132" s="7"/>
+      <c r="AC132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARGEST SINGLE AGGREGATE PROGRAMME IN THE COUNTRY. Procurement runs through NIPDEC (ECO-0038), so register there first, then track PURE tender notices directly.</t>
+        </is>
+      </c>
+      <c r="AE132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Road rehabilitation, slope stabilisation and bridge reconstruction consume pitrun, base aggregate and gravel at national scale. The Moruga Road upgrade alone was reported at $178M. PURE is the demand engine behind much of the country's aggregate consumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0128</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Water and Sewerage Authority (WASA)</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State water and wastewater utility</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Head office St Joseph; nationwide operations</t>
+        </is>
+      </c>
+      <c r="I133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.wasa.gov.tt/</t>
+        </is>
+      </c>
+      <c r="Q133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Web Search (public index)</t>
+        </is>
+      </c>
+      <c r="R133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.wasa.gov.tt/</t>
+        </is>
+      </c>
+      <c r="S133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sole national water and sewerage provider. Pipeline installation, leak repair, trench reinstatement and landslip restoration all require backfill and granular material continuously.</t>
+        </is>
+      </c>
+      <c r="T133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB133" s="7"/>
+      <c r="AC133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identify WASA's supplier registration route. Trench reinstatement is a continuous, nationwide backfill and sandfill requirement, which matches EcoEnergy's two newly priced lines.</t>
+        </is>
+      </c>
+      <c r="AE133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Founded 1965. Reported works include shoring, repacking material and rolling, which is exactly backfill and granular fill demand. A standing requirement rather than a project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0129</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Point Lisas Industrial Port Development Corporation (PLIPDECO)</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial estate landlord and port operator</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Point Lisas, Couva</t>
+        </is>
+      </c>
+      <c r="I134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.facebook.com/p/Point-Lisas-Industrial-Port-Development-Corporation-Limited-61576729882584/</t>
+        </is>
+      </c>
+      <c r="M134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.plipdeco.com/main/</t>
+        </is>
+      </c>
+      <c r="Q134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Web Search (public index)</t>
+        </is>
+      </c>
+      <c r="R134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.plipdeco.com/main/</t>
+        </is>
+      </c>
+      <c r="S134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Owner and landlord of the 860-hectare Point Lisas Industrial Estate with 103+ tenants, plus a six-berth port. Estate and port infrastructure works consume fill and aggregate.</t>
+        </is>
+      </c>
+      <c r="T134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB134" s="7"/>
+      <c r="AC134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approach on estate infrastructure and port works. Also treat as a channel: 103 tenants on one estate, each with their own civil works.</t>
+        </is>
+      </c>
+      <c r="AE134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. 51% state owned, 49% private. Couva location, the top section 18 priority area. The tenant base is a route to many industrial buyers through one relationship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0130</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heritage Petroleum Company Limited</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State onshore oil producer</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newtown, Port of Spain; onshore fields in south Trinidad</t>
+        </is>
+      </c>
+      <c r="I135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://heritage.co.tt/</t>
+        </is>
+      </c>
+      <c r="Q135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Web Search (public index)</t>
+        </is>
+      </c>
+      <c r="R135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://heritage.co.tt/prequalification-of-contractors-and-suppliers/</t>
+        </is>
+      </c>
+      <c r="S135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREQUALIFICATION PAGE CONFIRMED for contractors and suppliers. Accounts for around 55% of onshore production, and onshore fields require lease roads, well pads and access roads, all built on pitrun and granular fill.</t>
+        </is>
+      </c>
+      <c r="T135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB135" s="7"/>
+      <c r="AC135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMPLETE THE PREQUALIFICATION. Heritage publishes a formal supplier prequalification route and its award-of-contracts records, so the process is transparent and open.</t>
+        </is>
+      </c>
+      <c r="AE135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Lease roads and well pads are pure pitrun and granular fill demand, sustained across the onshore acreage. The Lease Out / Farm Out programme adds many smaller independent operators, each with their own access road requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0131</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Veratech Engineering and Construction Company Limited (VECCL)</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy civil / marine contractor</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="I136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.veccl.com/</t>
+        </is>
+      </c>
+      <c r="Q136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Web Search (public index)</t>
+        </is>
+      </c>
+      <c r="R136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.veccl.com/</t>
+        </is>
+      </c>
+      <c r="S136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named Heritage Petroleum supplier for infrastructure development. A recent contract for subsea pipeline and riser installation was valued at TT$37,834,010.55.</t>
+        </is>
+      </c>
+      <c r="T136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB136" s="7"/>
+      <c r="AC136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify contact and approach on onshore civil and shore-works aggregate supply.</t>
+        </is>
+      </c>
+      <c r="AE136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Established November 2018. Contract values in the tens of millions indicate genuine materials purchasing power. Energy-sector civil contractor. These firms build lease roads, well pads, foundations and site infrastructure, all of which consume pitrun and granular fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0132</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vertech General Contracting Ltd</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy general contractor</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Fernando</t>
+        </is>
+      </c>
+      <c r="I137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.vertechltd-tt.com/</t>
+        </is>
+      </c>
+      <c r="Q137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Web Search (public index)</t>
+        </is>
+      </c>
+      <c r="R137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.vertechltd-tt.com/</t>
+        </is>
+      </c>
+      <c r="S137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named Heritage Petroleum contractor, established 2008, delivering engineering solutions.</t>
+        </is>
+      </c>
+      <c r="T137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB137" s="7"/>
+      <c r="AC137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify contact and qualify their civil works volume.</t>
+        </is>
+      </c>
+      <c r="AE137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. San Fernando base puts them in the southern energy corridor. Energy-sector civil contractor. These firms build lease roads, well pads, foundations and site infrastructure, all of which consume pitrun and granular fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0133</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrick Gordon's Construction</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy civil infrastructure contractor</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="I138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business Excellence (via public search index)</t>
+        </is>
+      </c>
+      <c r="R138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.bus-ex.com/article/heritage-petroleum-fueling-caribbean-nations-economic-growth</t>
+        </is>
+      </c>
+      <c r="S138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named as Heritage Petroleum's key supplier for CIVIL INFRASTRUCTURE, which is the single most aggregate-intensive category in that supply chain.</t>
+        </is>
+      </c>
+      <c r="T138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB138" s="7"/>
+      <c r="AC138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIGH FIT. Named specifically for civil infrastructure to the largest onshore producer. Verify contact and approach on pitrun and granular fill.</t>
+        </is>
+      </c>
+      <c r="AE138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Of all the Heritage suppliers named, this one is described in the terms closest to EcoEnergy's product. Energy-sector civil contractor. These firms build lease roads, well pads, foundations and site infrastructure, all of which consume pitrun and granular fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0134</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Esskay Construction Services</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy construction contractor</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="I139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business Excellence (via public search index)</t>
+        </is>
+      </c>
+      <c r="R139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.bus-ex.com/article/heritage-petroleum-fueling-caribbean-nations-economic-growth</t>
+        </is>
+      </c>
+      <c r="S139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named Heritage Petroleum contractor providing construction, maintenance and logistical support.</t>
+        </is>
+      </c>
+      <c r="T139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB139" s="7"/>
+      <c r="AC139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify contact and qualify the civil works share of their activity.</t>
+        </is>
+      </c>
+      <c r="AE139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Energy-sector civil contractor. These firms build lease roads, well pads, foundations and site infrastructure, all of which consume pitrun and granular fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0135</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inland and Offshore Contractors</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy construction contractor</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="I140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business Excellence (via public search index)</t>
+        </is>
+      </c>
+      <c r="R140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.bus-ex.com/article/heritage-petroleum-fueling-caribbean-nations-economic-growth</t>
+        </is>
+      </c>
+      <c r="S140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named Heritage Petroleum contractor providing construction, maintenance and logistical support.</t>
+        </is>
+      </c>
+      <c r="T140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB140" s="7"/>
+      <c r="AC140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify contact. The inland arm is the relevant one for aggregate.</t>
+        </is>
+      </c>
+      <c r="AE140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Energy-sector civil contractor. These firms build lease roads, well pads, foundations and site infrastructure, all of which consume pitrun and granular fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0136</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uniform Building Contractors Ltd (UBC)</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pipeline / civil contractor</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad</t>
+        </is>
+      </c>
+      <c r="I141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newsday (via public search index)</t>
+        </is>
+      </c>
+      <c r="R141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://newsday.co.tt/2026/01/23/privy-council-dismisses-contractors-claim-against-wasa/</t>
+        </is>
+      </c>
+      <c r="S141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design-and-build contractor on a WASA pipeline project covering roughly 28km from Rio Claro to Mayaro, valued at just over $28 million. Pipeline work is trench and backfill intensive.</t>
+        </is>
+      </c>
+      <c r="T141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB141" s="7"/>
+      <c r="AC141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify current trading status FIRST. The WASA contract was terminated in 2009 and a related claim reached the Privy Council, so confirm the company is active and solvent before any commercial effort.</t>
+        </is>
+      </c>
+      <c r="AE141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. CAUTION. Recorded for completeness because pipeline contractors are strong backfill buyers, but the litigation history and the 2009 termination mean creditworthiness must be checked before extending any terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0137</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPML Contractors Ltd</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Civil contractor</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suite 101, Ramoutar Building, Southern Main Road, Couva</t>
+        </is>
+      </c>
+      <c r="I142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T&amp;T Chamber of Industry &amp; Commerce directory (via public search index)</t>
+        </is>
+      </c>
+      <c r="R142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://membership.chamber.org.tt/list/ql/construction-1094</t>
+        </is>
+      </c>
+      <c r="S142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chamber-listed construction company in Couva.</t>
+        </is>
+      </c>
+      <c r="T142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB142" s="7"/>
+      <c r="AC142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify contact and qualify project pipeline. Couva is the top priority area.</t>
+        </is>
+      </c>
+      <c r="AE142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Chamber membership implies an established, verifiable business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0138</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alpha Engineering &amp; Design (2002) Ltd</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering / civil contractor</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atlantic Plaza, Atlantic Avenue, Couva</t>
+        </is>
+      </c>
+      <c r="I143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T&amp;T Chamber of Industry &amp; Commerce directory (via public search index)</t>
+        </is>
+      </c>
+      <c r="R143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://membership.chamber.org.tt/list/ql/construction-1094</t>
+        </is>
+      </c>
+      <c r="S143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chamber-listed engineering and design firm in Couva.</t>
+        </is>
+      </c>
+      <c r="T143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB143" s="7"/>
+      <c r="AC143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify contact. Design firms specify materials, so they influence purchases even where they do not buy directly.</t>
+        </is>
+      </c>
+      <c r="AE143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Possible SPECIFIER as well as buyer. Getting EcoEnergy material accepted in a specification is worth more than a single sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0139</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C &amp; Z Engineering Services Ltd</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering / civil contractor</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stephen Street &amp; Southern Main Road, California, Couva</t>
+        </is>
+      </c>
+      <c r="I144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="Q144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T&amp;T Chamber of Industry &amp; Commerce directory (via public search index)</t>
+        </is>
+      </c>
+      <c r="R144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://membership.chamber.org.tt/list/ql/construction-1094</t>
+        </is>
+      </c>
+      <c r="S144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chamber-listed engineering services firm in the Couva corridor.</t>
+        </is>
+      </c>
+      <c r="T144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB144" s="7"/>
+      <c r="AC144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify contact and qualify civil works volume.</t>
+        </is>
+      </c>
+      <c r="AE144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. Couva corridor, priority area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0140</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEMCCO Ltd</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not publicly listed</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Civil / construction contractor</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - STRONG</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#402 Southern Main Road, La Romaine, San Fernando</t>
+        </is>
+      </c>
+      <c r="I145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="J145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="K145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="L145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="M145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="N145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="O145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING VERIFICATION</t>
+        </is>
+      </c>
+      <c r="P145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://hemcco.com/</t>
+        </is>
+      </c>
+      <c r="Q145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Web Search (public index)</t>
+        </is>
+      </c>
+      <c r="R145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://hemcco.com/</t>
+        </is>
+      </c>
+      <c r="S145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Established construction firm in the southern corridor with its own web presence.</t>
+        </is>
+      </c>
+      <c r="T145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pitrun; 3/8 gravel; 3/4 gravel; sharp sand; sandfill/backfill</t>
+        </is>
+      </c>
+      <c r="U145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A - consumes aggregate</t>
+        </is>
+      </c>
+      <c r="V145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EST - to confirm</t>
+        </is>
+      </c>
+      <c r="W145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To establish</t>
+        </is>
+      </c>
+      <c r="X145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not published</t>
+        </is>
+      </c>
+      <c r="Y145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per current EcoEnergy price list (see WEEKLY PRICING)</t>
+        </is>
+      </c>
+      <c r="Z145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Up to 30% subject to qualification</t>
+        </is>
+      </c>
+      <c r="AA145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISCOVERED</t>
+        </is>
+      </c>
+      <c r="AB145" s="7"/>
+      <c r="AC145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify contact and qualify project pipeline.</t>
+        </is>
+      </c>
+      <c r="AE145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYCLE 5 (2026-09-12), public sector and energy sweep. La Romaine and San Fernando are section 18 priority areas.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:AE117"/>
+  <autoFilter ref="A5:AE145"/>
 </worksheet>
 </file>
 
@@ -17134,7 +21418,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 5   |   12 September 2026  04:51 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 6   |   12 September 2026  05:47 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -17474,7 +21758,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 5   |   12 September 2026  04:51 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 6   |   12 September 2026  05:47 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -17962,7 +22246,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 5   |   12 September 2026  04:51 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 6   |   12 September 2026  05:47 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -19818,7 +24102,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -19836,7 +24120,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 5   |   12 September 2026  04:51 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 6   |   12 September 2026  05:47 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -19915,438 +24199,442 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total discovered today</t>
+          <t xml:space="preserve">New prospects discovered, cycle 5</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daily target is 25.</t>
+          <t xml:space="preserve">Public sector, utility and energy sweep. 14 municipal corporations, PURE, WASA, PLIPDECO, Heritage Petroleum and their civil contractors.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daily target</t>
+          <t xml:space="preserve">Total discovered today</t>
         </is>
       </c>
       <c r="B10" s="3">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brief section 1.</t>
+          <t xml:space="preserve">Daily target is 25.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Performance against daily target</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">404%</t>
-        </is>
+          <t xml:space="preserve">Daily target</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <v>25</v>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quality gate applied - no filler records.</t>
+          <t xml:space="preserve">Brief section 1.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carried forward from prior canon</t>
-        </is>
-      </c>
-      <c r="B12" s="3">
-        <v>11</v>
+          <t xml:space="preserve">Performance against daily target</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">516%</t>
+        </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merged from the previous EcoEnergy workbook on 2026-09-12. Not counted against the daily target.</t>
+          <t xml:space="preserve">Quality gate applied - no filler records.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duplicates avoided on merge</t>
+          <t xml:space="preserve">Carried forward from prior canon</t>
         </is>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concrete Aggregate Suppliers was already held as ECO-0006 and was updated, not duplicated (section 10).</t>
+          <t xml:space="preserve">Merged from the previous EcoEnergy workbook on 2026-09-12. Not counted against the daily target.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Duplicates avoided on merge</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Concrete Aggregate Suppliers was already held as ECO-0006 and was updated, not duplicated (section 10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Total prospects in pipeline</t>
         </is>
       </c>
-      <c r="B14" s="3">
-        <v>112</v>
-      </c>
-      <c r="C14" s="7"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="B15" s="3">
+        <v>140</v>
+      </c>
+      <c r="C15" s="7"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">BY PRIORITY</t>
         </is>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TIER 1</t>
-        </is>
-      </c>
-      <c r="B16" s="3">
-        <v>50</v>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Highest-value recurring buyers and resellers.</t>
-        </is>
-      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIER 2</t>
+          <t xml:space="preserve">TIER 1</t>
         </is>
       </c>
       <c r="B17" s="3">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary commercial buyers.</t>
+          <t xml:space="preserve">Highest-value recurring buyers and resellers.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIER 3</t>
+          <t xml:space="preserve">TIER 2</t>
         </is>
       </c>
       <c r="B18" s="3">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low-volume but steady.</t>
+          <t xml:space="preserve">Secondary commercial buyers.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">TIER 3</t>
+        </is>
+      </c>
+      <c r="B19" s="3">
+        <v>14</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low-volume but steady.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">BENCHMARK</t>
         </is>
       </c>
-      <c r="B19" s="3">
+      <c r="B20" s="3">
         <v>10</v>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Competitors and price references, not buyers.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">LEAD GRADE (brief section 11)</t>
         </is>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A - HOT</t>
-        </is>
-      </c>
-      <c r="B21" s="3">
-        <v>0</v>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Explicit current buying requirement with material, quantity or location identifiable. ZERO. Grade A requires reading comment threads, and no social platform was accessible.</t>
-        </is>
-      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">B - STRONG</t>
+          <t xml:space="preserve">A - HOT</t>
         </is>
       </c>
       <c r="B22" s="3">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verifiably consumes or resells aggregate. This is the working list.</t>
+          <t xml:space="preserve">Explicit current buying requirement with material, quantity or location identifiable. ZERO. Grade A requires reading comment threads, and no social platform was accessible.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">C - POTENTIAL</t>
+          <t xml:space="preserve">B - STRONG</t>
         </is>
       </c>
       <c r="B23" s="3">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construction-related, no current requirement verified.</t>
+          <t xml:space="preserve">Verifiably consumes or resells aggregate. This is the working list.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">C - POTENTIAL</t>
+        </is>
+      </c>
+      <c r="B24" s="3">
+        <v>45</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Construction-related, no current requirement verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">D - MARKET INTELLIGENCE</t>
         </is>
       </c>
-      <c r="B24" s="3">
+      <c r="B25" s="3">
         <v>11</v>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Competitors, licensed quarries and price references, not buyers.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">BY SEGMENT</t>
         </is>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ready-mix and block producers</t>
-        </is>
-      </c>
-      <c r="B26" s="3">
-        <v>13</v>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Highest continuous aggregate draw.</t>
-        </is>
-      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hardware stores and building-material resellers</t>
+          <t xml:space="preserve">Ready-mix and block producers</t>
         </is>
       </c>
       <c r="B27" s="3">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Already sell aggregate, therefore already buy it.</t>
+          <t xml:space="preserve">Highest continuous aggregate draw.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contractors, civil, earthworks and drainage</t>
+          <t xml:space="preserve">Hardware stores and building-material resellers</t>
         </is>
       </c>
       <c r="B28" s="3">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Project-driven volume.</t>
+          <t xml:space="preserve">Already sell aggregate, therefore already buy it.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">State developers and agencies</t>
+          <t xml:space="preserve">Contractors, civil, earthworks and drainage</t>
         </is>
       </c>
       <c r="B29" s="3">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tender and vendor registration route.</t>
+          <t xml:space="preserve">Project-driven volume.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trucking and haulage</t>
+          <t xml:space="preserve">State developers and agencies</t>
         </is>
       </c>
       <c r="B30" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buyers and potential delivery partners.</t>
+          <t xml:space="preserve">Tender and vendor registration route.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trucking and haulage</t>
+        </is>
+      </c>
+      <c r="B31" s="3">
+        <v>7</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buyers and potential delivery partners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Landscaping</t>
         </is>
       </c>
-      <c r="B31" s="3">
+      <c r="B32" s="3">
         <v>5</v>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Batch into one campaign.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">COMMERCIAL ACTIVITY</t>
         </is>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prospects with a verified contact route</t>
-        </is>
-      </c>
-      <c r="B33" s="3">
-        <v>15</v>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">All carried forward from prior canon. Telephone and e-mail for these were verified previously, not by this cycle's searches.</t>
-        </is>
-      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prospects with NO contact route</t>
+          <t xml:space="preserve">Prospects with a verified contact route</t>
         </is>
       </c>
       <c r="B34" s="3">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sourced and named, but no number or address could be verified from this environment. None invented.</t>
+          <t xml:space="preserve">All carried forward from prior canon. Telephone and e-mail for these were verified previously, not by this cycle's searches.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outreach messages sent</t>
+          <t xml:space="preserve">Prospects with NO contact route</t>
         </is>
       </c>
       <c r="B35" s="3">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cumosco and KAMCO, both by e-mail on 2026-09-12. Prior canon. This agent sent nothing.</t>
+          <t xml:space="preserve">Sourced and named, but no number or address could be verified from this environment. None invented.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Responses received</t>
+          <t xml:space="preserve">Outreach messages sent</t>
         </is>
       </c>
       <c r="B36" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Both outbound e-mails are still pending a reply.</t>
+          <t xml:space="preserve">Cumosco and KAMCO, both by e-mail on 2026-09-12. Prior canon. This agent sent nothing.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quote requests</t>
+          <t xml:space="preserve">Responses received</t>
         </is>
       </c>
       <c r="B37" s="3">
         <v>0</v>
       </c>
-      <c r="C37" s="7"/>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Both outbound e-mails are still pending a reply.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quotes issued</t>
+          <t xml:space="preserve">Quote requests</t>
         </is>
       </c>
       <c r="B38" s="3">
-        <v>1</v>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cumosco was quoted TT$125 / 195 / 205 per yd3 on 2026-09-12.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C38" s="7"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negotiations open</t>
+          <t xml:space="preserve">Quotes issued</t>
         </is>
       </c>
       <c r="B39" s="3">
-        <v>0</v>
-      </c>
-      <c r="C39" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cumosco was quoted TT$125 / 195 / 205 per yd3 on 2026-09-12.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customers won</t>
+          <t xml:space="preserve">Negotiations open</t>
         </is>
       </c>
       <c r="B40" s="3">
@@ -20355,366 +24643,360 @@
       <c r="C40" s="7"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customers won</t>
+        </is>
+      </c>
+      <c r="B41" s="3">
+        <v>0</v>
+      </c>
+      <c r="C41" s="7"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">PRICING EXCEPTION - ACTION REQUIRED</t>
         </is>
       </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cumosco quotation above list price</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CORRECTION DUE</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026-09-12 quote of TT$125 / 195 / 205 per yd3 for pitrun / 3/8 / 3/4 sits ABOVE the canon list price of TT$77.63 / 167.06 / 167.06. Owner ruled on 2026-09-12 that the price list is canon, so a corrected quotation must be issued to Cumosco before any follow-up.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">PRICING</t>
         </is>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Materials with an EcoEnergy base price</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 of 7</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3/4 gravel, 3/8 gravel, sharp sand, plastering sand.</t>
-        </is>
-      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Materials flagged MARKET VERIFICATION REQUIRED</t>
-        </is>
-      </c>
-      <c r="B45" s="3">
-        <v>0</v>
+          <t xml:space="preserve">Materials with an EcoEnergy base price</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 of 7</t>
+        </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pitrun and sandfill/backfill - no published T&amp;T price found.</t>
+          <t xml:space="preserve">3/4 gravel, 3/8 gravel, sharp sand, plastering sand.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pricing rule applied</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Benchmark x 0.90</t>
-        </is>
+          <t xml:space="preserve">Materials flagged MARKET VERIFICATION REQUIRED</t>
+        </is>
+      </c>
+      <c r="B46" s="3">
+        <v>0</v>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">10% below verified market benchmark.</t>
+          <t xml:space="preserve">Pitrun and sandfill/backfill - no published T&amp;T price found.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maximum negotiated discount</t>
+          <t xml:space="preserve">Pricing rule applied</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30%</t>
+          <t xml:space="preserve">Benchmark x 0.90</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Closing tool. Never automatic, never advertised.</t>
+          <t xml:space="preserve">10% below verified market benchmark.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Maximum negotiated discount</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30%</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Closing tool. Never automatic, never advertised.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Next scheduled market review</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-13 23:59 (Sunday, Trinidad time, AST/UTC-4)</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Brief section 6.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">CHANNEL ACCESS - VERIFIED THIS CYCLE</t>
         </is>
       </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Metricool MCP connector</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONNECTED</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Authenticated and responding. It returned 4 brands, all personal or Iseldoran Sagas accounts: kerron.pierre5, thekerron, kerron347, kerron.shaul.pier and IseldoranSagas.</t>
-        </is>
-      </c>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy brand in Metricool</t>
+          <t xml:space="preserve">Metricool MCP connector</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">STILL NOT PRESENT</t>
+          <t xml:space="preserve">DISCONNECTED</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">No EcoEnergy brand exists. On owner instruction the kerron.pierre5 brand was used instead to publish the EcoEnergy offer.</t>
+          <t xml:space="preserve">The Metricool MCP server is no longer connected to this session and its tools cannot be called. The post scheduled on 2026-09-12 (id 374817136) was confirmed in the planner when created and is still expected to publish 2026-09-14 at 11:00 Trinidad time, but that can no longer be verified from here. Check the accounts directly or reopen Metricool.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduled post via kerron.pierre5</t>
+          <t xml:space="preserve">Metricool, when it was connected</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONFIRMED</t>
+          <t xml:space="preserve">CONNECTED</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post id 374817136 scheduled for 2026-09-14 11:00 Trinidad time (17:00 Europe/Madrid) to Facebook, LinkedIn and Threads, autoPublish on. Tool returned status PENDING on all three. SCHEDULED, NOT YET PUBLISHED.</t>
+          <t xml:space="preserve">Authenticated and responding. It returned 4 brands, all personal or Iseldoran Sagas accounts: kerron.pierre5, thekerron, kerron347, kerron.shaul.pier and IseldoranSagas.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Networks excluded from that post</t>
+          <t xml:space="preserve">EcoEnergy brand in Metricool</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">STILL NOT PRESENT</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instagram, TikTok and YouTube require an image or video and none was available. X was excluded because that handle is IseldoranSagas, a separate novel brand.</t>
+          <t xml:space="preserve">No EcoEnergy brand exists. On owner instruction the kerron.pierre5 brand was used instead to publish the EcoEnergy offer.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricool competitor tracking</t>
+          <t xml:space="preserve">Scheduled post via kerron.pierre5</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPTY</t>
+          <t xml:space="preserve">CONFIRMED</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Queried for the brand over the last 30 days and returned no rows, because no competitors are configured. This is Metricool's only third-party data surface.</t>
+          <t xml:space="preserve">Post id 374817136 scheduled for 2026-09-14 11:00 Trinidad time (17:00 Europe/Madrid) to Facebook, LinkedIn and Threads, autoPublish on. Tool returned status PENDING on all three. SCHEDULED, NOT YET PUBLISHED.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricool as a prospecting tool</t>
+          <t xml:space="preserve">Networks excluded from that post</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT CAPABLE</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Its toolset is scheduling, analytics and best-time-to-post for accounts you own. It cannot search Facebook, Instagram, TikTok, X or Threads for third-party prospects or prices. Its only third-party feature is competitor tracking on Instagram, Facebook, Twitch, YouTube, X and Bluesky, and that needs an EcoEnergy brand first.</t>
+          <t xml:space="preserve">Instagram, TikTok and YouTube require an image or video and none was available. X was excluded because that handle is IseldoranSagas, a separate novel brand.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facebook / Instagram / TikTok / X / Threads</t>
+          <t xml:space="preserve">Metricool competitor tracking</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLATFORM NOT ACCESSIBLE</t>
+          <t xml:space="preserve">EMPTY</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Re-tested 2026-09-12. facebook.com, web.facebook.com, mbasic.facebook.com, instagram.com, tiktok.com, x.com, twitter.com and threads.net ALL returned 403 at the egress proxy. There is also no browser tool and no logged-in session in this environment.</t>
+          <t xml:space="preserve">Queried for the brand over the last 30 days and returned no rows, because no competitors are configured. This is Metricool's only third-party data surface.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facebook Marketplace</t>
+          <t xml:space="preserve">Metricool as a prospecting tool</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARKETPLACE - ACCESS UNAVAILABLE</t>
+          <t xml:space="preserve">NOT CAPABLE</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Listing data reached this pipeline only through public search indexing.</t>
+          <t xml:space="preserve">Its toolset is scheduling, analytics and best-time-to-post for accounts you own. It cannot search Facebook, Instagram, TikTok, X or Threads for third-party prospects or prices. Its only third-party feature is competitor tracking on Instagram, Facebook, Twitch, YouTube, X and Bluesky, and that needs an EcoEnergy brand first.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facebook groups</t>
+          <t xml:space="preserve">Facebook / Instagram / TikTok / X / Threads</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRIVATE / NOT ACCESSED</t>
+          <t xml:space="preserve">PLATFORM NOT ACCESSIBLE</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four active T&amp;T buyer groups identified by id but none could be opened: 909331405759624, 202165237740335, 339202526592121, 3250335484987349.</t>
+          <t xml:space="preserve">Re-tested 2026-09-12. facebook.com, web.facebook.com, mbasic.facebook.com, instagram.com, tiktok.com, x.com, twitter.com and threads.net ALL returned 403 at the egress proxy. There is also no browser tool and no logged-in session in this environment.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comment mining (brief section 3)</t>
+          <t xml:space="preserve">Facebook Marketplace</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMENTS - NOT ACCESSIBLE</t>
+          <t xml:space="preserve">MARKETPLACE - ACCESS UNAVAILABLE</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">No comment or reply thread was read on any platform. Zero grade A leads follow directly from this. The nearest accessible substitute found is the public Trinituner forum.</t>
+          <t xml:space="preserve">Listing data reached this pipeline only through public search indexing.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instagram / TikTok search yield</t>
+          <t xml:space="preserve">Facebook groups</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NIL FOR T&amp;T</t>
+          <t xml:space="preserve">PRIVATE / NOT ACCESSED</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Searches returned predominantly United States results, including Trinidad, Colorado businesses. Not evidence that no T&amp;T accounts exist, only that the public index did not surface them.</t>
+          <t xml:space="preserve">Four active T&amp;T buyer groups identified by id but none could be opened: 909331405759624, 202165237740335, 339202526592121, 3250335484987349.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MARKET INTELLIGENCE - CYCLE 2</t>
-        </is>
-      </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment mining (brief section 3)</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMENTS - NOT ACCESSIBLE</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No comment or reply thread was read on any platform. Zero grade A leads follow directly from this. The nearest accessible substitute found is the public Trinituner forum.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 quarries voluntarily shut in a licensing dispute</t>
+          <t xml:space="preserve">Instagram / TikTok search yield</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">NIL FOR T&amp;T</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">In November 2025 the newly formed Trinidad and Tobago Aggregate Producers Alliance (TTAPA) closed 24 member quarries nationwide over the Government's failure to issue overdue processing licences. TTAPA's president warned that as many as 100,000 construction jobs were at risk.  IMPLICATION: A supply shock in the aggregate market. Buyers who lost their supplier are actively looking for one. This is the strongest commercial opening available.</t>
+          <t xml:space="preserve">Searches returned predominantly United States results, including Trinidad, Colorado businesses. Not evidence that no T&amp;T accounts exist, only that the public index did not surface them.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aggregate shortfall feared as demand outruns production</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VERIFIED</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reporting describes a widening gap between aggregate demand and production capacity as major infrastructure projects move forward.  IMPLICATION: Demand-led market. Supply reliability outranks price for many buyers, which supports holding the base price rather than discounting early.</t>
-        </is>
-      </c>
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARKET INTELLIGENCE - CYCLE 2</t>
+        </is>
+      </c>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Licensing structure: 9 full licences, the rest on hold-over permits</t>
+          <t xml:space="preserve">24 quarries voluntarily shut in a licensing dispute</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -20724,14 +25006,14 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nine companies hold full licences to mine or process aggregate. Another 13 operate under temporary hold-over permits granted by the line minister. The Ministry states 25 bona fide operators received hold-over letters on 22 May.  IMPLICATION: Licence status is now a commercial differentiator. A buyer facing a police crackdown on illegal material wants a supplier whose paperwork is sound.</t>
+          <t xml:space="preserve">In November 2025 the newly formed Trinidad and Tobago Aggregate Producers Alliance (TTAPA) closed 24 member quarries nationwide over the Government's failure to issue overdue processing licences. TTAPA's president warned that as many as 100,000 construction jobs were at risk.  IMPLICATION: A supply shock in the aggregate market. Buyers who lost their supplier are actively looking for one. This is the strongest commercial opening available.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Police crackdown on illegal quarries</t>
+          <t xml:space="preserve">Aggregate shortfall feared as demand outruns production</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -20741,14 +25023,14 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newsday reported in November 2025 that police moved against illegal quarrying operations.  IMPLICATION: Buyers sourcing from unlicensed operators carry real risk. Licensed supply is worth a premium to any contractor on a government project.</t>
+          <t xml:space="preserve">Reporting describes a widening gap between aggregate demand and production capacity as major infrastructure projects move forward.  IMPLICATION: Demand-led market. Supply reliability outranks price for many buyers, which supports holding the base price rather than discounting early.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Named licensed quarry operations</t>
+          <t xml:space="preserve">Licensing structure: 9 full licences, the rest on hold-over permits</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -20758,31 +25040,31 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reported licensed operations include Bestcrete (Melajo Forest Reserve, Matura), ANSA McAL (Depot Road, Longdenville), Mineral Mines of Trinidad (Vega de Oropouche), EMBD (Coco Road, Claxton Bay and Milton Village, Couva), AADS Multi-Tasking (Rio Grande Trace, Matura), Firma Fabrication and Construction (Melajo Forest Reserve, Sangre Grande) and Seereeram Brothers (Cangrejal Road, Santa Cruz).  IMPLICATION: This is the competitor map. Seereeram Brothers was previously held as a contractor prospect and has been reclassified as a producer.</t>
+          <t xml:space="preserve">Nine companies hold full licences to mine or process aggregate. Another 13 operate under temporary hold-over permits granted by the line minister. The Ministry states 25 bona fide operators received hold-over letters on 22 May.  IMPLICATION: Licence status is now a commercial differentiator. A buyer facing a police crackdown on illegal material wants a supplier whose paperwork is sound.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN QUESTION: EcoEnergy's own licence status is not established</t>
+          <t xml:space="preserve">Police crackdown on illegal quarries</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT VERIFIED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The shortage and crackdown make licensed supply a strong selling position, but EcoEnergy's own licence or hold-over permit status is not recorded anywhere in this pipeline and was not supplied.  IMPLICATION: BLOCKING for the licence-led pitch. Confirm EcoEnergy's status before any outreach claims licensed supply. Do not make the claim until it is confirmed.</t>
+          <t xml:space="preserve">Newsday reported in November 2025 that police moved against illegal quarrying operations.  IMPLICATION: Buyers sourcing from unlicensed operators carry real risk. Licensed supply is worth a premium to any contractor on a government project.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricool competitor tracking returned no data</t>
+          <t xml:space="preserve">Named licensed quarry operations</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -20792,31 +25074,31 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The competitors connector was queried for the kerron.pierre5 brand over 2026-08-13 to 2026-09-12 for Facebook competitor screen name, display name, followers and posts. It returned an empty result set, because no competitors are configured on the brand.  IMPLICATION: Metricool's only third-party data surface is competitor tracking, and it is empty. Adding rival aggregate sellers as competitors would turn it into a genuine monitoring channel. It still cannot search for prospects or prices.</t>
+          <t xml:space="preserve">Reported licensed operations include Bestcrete (Melajo Forest Reserve, Matura), ANSA McAL (Depot Road, Longdenville), Mineral Mines of Trinidad (Vega de Oropouche), EMBD (Coco Road, Claxton Bay and Milton Village, Couva), AADS Multi-Tasking (Rio Grande Trace, Matura), Firma Fabrication and Construction (Melajo Forest Reserve, Sangre Grande) and Seereeram Brothers (Cangrejal Road, Santa Cruz).  IMPLICATION: This is the competitor map. Seereeram Brothers was previously held as a contractor prospect and has been reclassified as a producer.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Best-time-to-post data reflects the wrong audience</t>
+          <t xml:space="preserve">OPEN QUESTION: EcoEnergy's own licence status is not established</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERIFIED</t>
+          <t xml:space="preserve">NOT VERIFIED</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricool returned Facebook best-time data for the kerron.pierre5 brand. The strongest hours sit around 10:00 to 12:00 Europe/Madrid, which is 04:00 to 06:00 in Trinidad. The brand's timezone is set to Europe/Madrid and its audience is the existing personal and Iseldoran Sagas following, not Trinidad construction buyers.  IMPLICATION: The engagement peaks are not a guide for a Trinidad B2B audience. The post was instead scheduled at 17:00 Madrid, which is 11:00 Trinidad, the strongest hour in the data that still falls inside Trinidad business hours. Set the brand timezone to America/Port_of_Spain if EcoEnergy will keep using it.</t>
+          <t xml:space="preserve">The shortage and crackdown make licensed supply a strong selling position, but EcoEnergy's own licence or hold-over permit status is not recorded anywhere in this pipeline and was not supplied.  IMPLICATION: BLOCKING for the licence-led pitch. Confirm EcoEnergy's status before any outreach claims licensed supply. Do not make the claim until it is confirmed.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRICING GAP: the delivered market may sit far above the EcoEnergy base</t>
+          <t xml:space="preserve">Metricool competitor tracking returned no data</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -20826,14 +25108,14 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy's base is derived from the Bestcrete published figure of TT$185.62/yd3, giving TT$167.06. Cycle 4 captured delivered and retail load pricing well above that: AMCOL crusher run at TT$375/yd3, forum-reported half-and-half gravel at about TT$275/yd3, NARS sharp sand at TT$450/yd and AMCOL sharp sand at TT$440/yd.  IMPLICATION: Section 10 forbids undercutting delivered retail with an ex-quarry product, and that rule protects EcoEnergy here. The TT$167.06 base is an EX-QUARRY COLLECTION price and should stay that way. A SEPARATE DELIVERED price list should be built against the TT$275 to TT$375/yd3 delivered band. Quoting the collection base to a delivered customer gives away the entire haulage margin.</t>
+          <t xml:space="preserve">The competitors connector was queried for the kerron.pierre5 brand over 2026-08-13 to 2026-09-12 for Facebook competitor screen name, display name, followers and posts. It returned an empty result set, because no competitors are configured on the brand.  IMPLICATION: Metricool's only third-party data surface is competitor tracking, and it is empty. Adding rival aggregate sellers as competitors would turn it into a genuine monitoring channel. It still cannot search for prospects or prices.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buyer demand is concentrated in Facebook groups and a public forum</t>
+          <t xml:space="preserve">Best-time-to-post data reflects the wrong audience</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -20843,14 +25125,14 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four active Trinidad buyer venues were identified: Facebook groups 909331405759624, 202165237740335, 339202526592121 and 3250335484987349, plus the Trinituner forum, where threads carry explicit price questions such as 'What is the average price of ready mix concrete per meter?'.  IMPLICATION: The forum is the one venue that may be readable without a login. It is the highest-value unmined source and should be worked first by anyone with ordinary web access.</t>
+          <t xml:space="preserve">Metricool returned Facebook best-time data for the kerron.pierre5 brand. The strongest hours sit around 10:00 to 12:00 Europe/Madrid, which is 04:00 to 06:00 in Trinidad. The brand's timezone is set to Europe/Madrid and its audience is the existing personal and Iseldoran Sagas following, not Trinidad construction buyers.  IMPLICATION: The engagement peaks are not a guide for a Trinidad B2B audience. The post was instead scheduled at 17:00 Madrid, which is 11:00 Trinidad, the strongest hour in the data that still falls inside Trinidad business hours. Set the brand timezone to America/Port_of_Spain if EcoEnergy will keep using it.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instagram and TikTok returned no usable Trinidad &amp; Tobago results</t>
+          <t xml:space="preserve">PRICING GAP: the delivered market may sit far above the EcoEnergy base</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -20860,116 +25142,184 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Searches on Instagram and TikTok terms returned predominantly United States results, including Trinidad, Colorado businesses and a US 'Trinidad Construction LLC'. No Trinidad &amp; Tobago aggregate buyer or seller was identified on either platform.  IMPLICATION: Not evidence that no such accounts exist. It reflects what the public search index surfaces without platform access. Both platforms remain unmined.</t>
+          <t xml:space="preserve">EcoEnergy's base is derived from the Bestcrete published figure of TT$185.62/yd3, giving TT$167.06. Cycle 4 captured delivered and retail load pricing well above that: AMCOL crusher run at TT$375/yd3, forum-reported half-and-half gravel at about TT$275/yd3, NARS sharp sand at TT$450/yd and AMCOL sharp sand at TT$440/yd.  IMPLICATION: Section 10 forbids undercutting delivered retail with an ex-quarry product, and that rule protects EcoEnergy here. The TT$167.06 base is an EX-QUARRY COLLECTION price and should stay that way. A SEPARATE DELIVERED price list should be built against the TT$275 to TT$375/yd3 delivered band. Quoting the collection base to a delivered customer gives away the entire haulage margin.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BLOCKERS - REQUIRE HUMAN ACTION</t>
-        </is>
-      </c>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buyer demand is concentrated in Facebook groups and a public forum</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VERIFIED</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Four active Trinidad buyer venues were identified: Facebook groups 909331405759624, 202165237740335, 339202526592121 and 3250335484987349, plus the Trinituner forum, where threads carry explicit price questions such as 'What is the average price of ready mix concrete per meter?'.  IMPLICATION: The forum is the one venue that may be readable without a login. It is the highest-value unmined source and should be worked first by anyone with ordinary web access.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Contact details for the discovered prospects</t>
+          <t xml:space="preserve">Instagram and TikTok returned no usable Trinidad &amp; Tobago results</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLOCKING</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">97 of 112 prospects have no verified contact route. Directory and company pages (findyello.com, nqcl.co.tt, energy.gov.tt, tt.directory) are refused by the egress proxy. Allowlist those hosts, or supply the details from a machine with ordinary web access.</t>
+          <t xml:space="preserve">Searches on Instagram and TikTok terms returned predominantly United States results, including Trinidad, Colorado businesses and a US 'Trinidad Construction LLC'. No Trinidad &amp; Tobago aggregate buyer or seller was identified on either platform.  IMPLICATION: Not evidence that no such accounts exist. It reflects what the public search index surfaces without platform access. Both platforms remain unmined.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Messaging integration</t>
+          <t xml:space="preserve">The public sector is the largest unworked aggregate demand in the pipeline</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLOCKING</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">No authorised e-mail or messaging tool is connected to this agent. The two e-mails on record were sent outside it, through Outlook. Until an integration is authorised, outreach cannot be executed here even for the 15 prospects that do have a contact route.</t>
+          <t xml:space="preserve">Fourteen municipal corporations each hold statutory responsibility for local roads and bridges and for drainage and irrigation, with annual budgets. Above them sit the MOWT PURE road rehabilitation programme, procured through NIPDEC since 2002, and WASA's continuous trench reinstatement. Heritage Petroleum publishes an open supplier prequalification route for its onshore lease road and well pad works.  IMPLICATION: This demand is recurring and annually funded rather than project-driven, which is exactly the recurring volume the brief targets. It is reached by SUPPLIER REGISTRATION, not cold selling, so the work is paperwork done once that then admits EcoEnergy to years of tenders. NIPDEC registration is the highest-leverage single action because it gates the national road programme.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. NQCL price list PDF</t>
+          <t xml:space="preserve">Metricool connector has disconnected from this session</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTIALLY RESOLVED</t>
+          <t xml:space="preserve">VERIFIED</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The pitrun benchmark of TT$86.25/yd3 was recovered from prior canon, so pitrun is now priced. The PDF itself is still blocked, and it is effective 31-Aug-2022, so the benchmark is four years old.</t>
+          <t xml:space="preserve">The Metricool MCP server is no longer connected. Its tools cannot be called. The post scheduled on 2026-09-12 for the kerron.pierre5 brand, id 374817136, was confirmed present in the planner at the time it was created and is still expected to publish on 2026-09-14 at 11:00 Trinidad time, but that can no longer be verified from this session.  IMPLICATION: Verify the post published by checking the Facebook, LinkedIn and Threads accounts directly, or by reopening Metricool. Do not assume delivery.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4. Social comment mining</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOT ACCESSIBLE</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Facebook, Instagram, X and Threads are not reachable from this environment. Section 4 comment mining could not be run beyond what public search indexes surfaced. Three active T&amp;T buyer groups were located and are named in the weekly report for someone with Facebook access to mine.</t>
-        </is>
-      </c>
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKERS - REQUIRE HUMAN ACTION</t>
+        </is>
+      </c>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. EcoEnergy quarry licence status</t>
+          <t xml:space="preserve">1. Contact details for the discovered prospects</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLOCKING THE STRONGEST PITCH</t>
+          <t xml:space="preserve">BLOCKING</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 quarries shut in a licensing dispute and police are acting against illegal operations, which makes licensed supply a powerful selling position. EcoEnergy's own licence or hold-over permit status is not recorded anywhere and was not supplied. Do NOT claim licensed supply in outreach until confirmed.</t>
+          <t xml:space="preserve">125 of 140 prospects have no verified contact route. Directory and company pages (findyello.com, nqcl.co.tt, energy.gov.tt, tt.directory) are refused by the egress proxy. Allowlist those hosts, or supply the details from a machine with ordinary web access.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">2. Messaging integration</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKING</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No authorised e-mail or messaging tool is connected to this agent. The two e-mails on record were sent outside it, through Outlook. Until an integration is authorised, outreach cannot be executed here even for the 15 prospects that do have a contact route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. NQCL price list PDF</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIALLY RESOLVED</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The pitrun benchmark of TT$86.25/yd3 was recovered from prior canon, so pitrun is now priced. The PDF itself is still blocked, and it is effective 31-Aug-2022, so the benchmark is four years old.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Social comment mining</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT ACCESSIBLE</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facebook, Instagram, X and Threads are not reachable from this environment. Section 4 comment mining could not be run beyond what public search indexes surfaced. Three active T&amp;T buyer groups were located and are named in the weekly report for someone with Facebook access to mine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. EcoEnergy quarry licence status</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCKING THE STRONGEST PITCH</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 quarries shut in a licensing dispute and police are acting against illegal operations, which makes licensed supply a powerful selling position. EcoEnergy's own licence or hold-over permit status is not recorded anywhere and was not supplied. Do NOT claim licensed supply in outreach until confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">6. Metricool EcoEnergy brand</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ACTION</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Create an EcoEnergy brand in Metricool and connect its Facebook and Instagram pages. That enables competitor tracking on rival aggregate sellers and gives EcoEnergy an inbound lead channel.</t>
         </is>
@@ -20981,7 +25331,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -21003,7 +25353,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 5   |   12 September 2026  04:51 (Trinidad time)</t>
+          <t xml:space="preserve">EcoEnergy Limited, Trinidad &amp; Tobago   |   Edition 1 Version 6   |   12 September 2026  05:47 (Trinidad time)</t>
         </is>
       </c>
     </row>
@@ -22439,7 +26789,7 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIER 2</t>
+          <t xml:space="preserve">TIER 1</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -25196,50 +29546,1086 @@
         </is>
       </c>
     </row>
-    <row r="118"/>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0113</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couva/Tabaquite/Talparo Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROCUREMENT PAGE CONFIRMED, listing categories 'Drainage and Irrigation' and 'Local Roads and Bridges'. The clearest documented public-sector aggregate requirement found so far. Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+    </row>
     <row r="119">
-      <c r="A119" s="6" t="inlineStr">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0114</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sangre Grande Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Discovered this cycle</t>
         </is>
       </c>
-      <c r="B119" s="3">
-        <v>101</v>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="6" t="inlineStr">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0115</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penal/Debe Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0116</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Princes Town Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0117</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chaguanas Borough Corporation</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0118</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arima Borough Corporation</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0119</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Fernando City Corporation</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0120</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Port of Spain City Corporation</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0121</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diego Martin Borough Corporation</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0122</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Siparia Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0123</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Juan/Laventille Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0124</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tunapuna/Piarco Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0125</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mayaro/Rio Claro Regional Corporation</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0126</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Point Fortin Borough Corporation</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Municipal corporation - local roads and drainage</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statutory responsibility for LOCAL ROADS AND BRIDGES and for DRAINAGE AND IRRIGATION. Both are annually funded, recurring aggregate requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0127</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ministry of Works and Transport - PURE Unit</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">National road rehabilitation programme</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme for Upgrading Roads Efficiency. Tenders cover slope stabilisation, road work, bridge reconstruction and alternative access routes, all heavy aggregate consumers. Has a live procurement page inviting contractors to tender.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0128</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Water and Sewerage Authority (WASA)</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State water and wastewater utility</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sole national water and sewerage provider. Pipeline installation, leak repair, trench reinstatement and landslip restoration all require backfill and granular material continuously.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0129</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Point Lisas Industrial Port Development Corporation (PLIPDECO)</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial estate landlord and port operator</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Owner and landlord of the 860-hectare Point Lisas Industrial Estate with 103+ tenants, plus a six-berth port. Estate and port infrastructure works consume fill and aggregate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0130</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heritage Petroleum Company Limited</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State onshore oil producer</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREQUALIFICATION PAGE CONFIRMED for contractors and suppliers. Accounts for around 55% of onshore production, and onshore fields require lease roads, well pads and access roads, all built on pitrun and granular fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0131</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Veratech Engineering and Construction Company Limited (VECCL)</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy civil / marine contractor</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named Heritage Petroleum supplier for infrastructure development. A recent contract for subsea pipeline and riser installation was valued at TT$37,834,010.55.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0132</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vertech General Contracting Ltd</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy general contractor</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named Heritage Petroleum contractor, established 2008, delivering engineering solutions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0133</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrick Gordon's Construction</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 1</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy civil infrastructure contractor</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named as Heritage Petroleum's key supplier for CIVIL INFRASTRUCTURE, which is the single most aggregate-intensive category in that supply chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0134</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Esskay Construction Services</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy construction contractor</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named Heritage Petroleum contractor providing construction, maintenance and logistical support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0135</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inland and Offshore Contractors</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy construction contractor</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named Heritage Petroleum contractor providing construction, maintenance and logistical support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0136</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uniform Building Contractors Ltd (UBC)</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pipeline / civil contractor</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design-and-build contractor on a WASA pipeline project covering roughly 28km from Rio Claro to Mayaro, valued at just over $28 million. Pipeline work is trench and backfill intensive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0137</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPML Contractors Ltd</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Civil contractor</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chamber-listed construction company in Couva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0138</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alpha Engineering &amp; Design (2002) Ltd</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering / civil contractor</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chamber-listed engineering and design firm in Couva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0139</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C &amp; Z Engineering Services Ltd</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering / civil contractor</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chamber-listed engineering services firm in the Couva corridor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-12</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECO-0140</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEMCCO Ltd</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER 2</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Civil / construction contractor</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Established construction firm in the southern corridor with its own web presence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146"/>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discovered this cycle</t>
+        </is>
+      </c>
+      <c r="B147" s="3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Merged from prior canon</t>
         </is>
       </c>
-      <c r="B120" s="3">
+      <c r="B148" s="3">
         <v>11</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="6" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Weekly target</t>
         </is>
       </c>
-      <c r="B121" s="3">
+      <c r="B149" s="3">
         <v>175</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="6" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Against weekly target (discovered only)</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58%</t>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G122"/>
+  <autoFilter ref="A5:G150"/>
 </worksheet>
 </file>